--- a/PartnerLive.xlsx
+++ b/PartnerLive.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Backup Backbone\New Bot\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aman\Desktop\Whatsapp-Bot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5BE7DB1-A136-4F17-8C09-97F37C8FFEC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05600A81-6EA6-4005-A0C0-C7EDFC88B0A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C75BA36E-5054-45D2-A98B-6C894BB3EF59}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$J$251</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$K$251</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1020" uniqueCount="707">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1271" uniqueCount="728">
   <si>
     <t>LOKESH BHAGAT</t>
   </si>
@@ -2158,6 +2158,69 @@
   </si>
   <si>
     <t>jh.rcd</t>
+  </si>
+  <si>
+    <t>District</t>
+  </si>
+  <si>
+    <t>Bokaro</t>
+  </si>
+  <si>
+    <t>Dhanbad</t>
+  </si>
+  <si>
+    <t>Giridih</t>
+  </si>
+  <si>
+    <t>Purbi Singhbhum</t>
+  </si>
+  <si>
+    <t>Sahibganj</t>
+  </si>
+  <si>
+    <t>Ranchi</t>
+  </si>
+  <si>
+    <t>Pashchimi Singhbhum</t>
+  </si>
+  <si>
+    <t>Dumka</t>
+  </si>
+  <si>
+    <t>Kodarma</t>
+  </si>
+  <si>
+    <t>Ramgarh</t>
+  </si>
+  <si>
+    <t>Khunti</t>
+  </si>
+  <si>
+    <t>Jamtara</t>
+  </si>
+  <si>
+    <t>Garhwa</t>
+  </si>
+  <si>
+    <t>Hazaribagh</t>
+  </si>
+  <si>
+    <t>Lohardaga</t>
+  </si>
+  <si>
+    <t>Deoghar</t>
+  </si>
+  <si>
+    <t>Saraikela-Kharsawan</t>
+  </si>
+  <si>
+    <t>Chatra</t>
+  </si>
+  <si>
+    <t>Pakur</t>
+  </si>
+  <si>
+    <t>Latehar</t>
   </si>
 </sst>
 </file>
@@ -2539,7 +2602,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF083C59-F580-442E-B6A4-AF176C2AA0E1}">
-  <dimension ref="A1:J251"/>
+  <dimension ref="A1:K251"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.42578125" bestFit="1" customWidth="1"/>
@@ -2547,14 +2610,15 @@
     <col min="3" max="3" width="14.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="28.42578125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="56.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="44.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="56.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="44.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>248</v>
       </c>
@@ -2571,22 +2635,25 @@
         <v>251</v>
       </c>
       <c r="F1" s="2" t="s">
+        <v>707</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>471</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>472</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>6863768803</v>
       </c>
@@ -2602,19 +2669,22 @@
       <c r="E2" s="3">
         <v>9631491612</v>
       </c>
-      <c r="F2" s="3">
+      <c r="F2" s="3" t="s">
+        <v>708</v>
+      </c>
+      <c r="G2" s="3">
         <v>828</v>
       </c>
-      <c r="G2" s="3">
+      <c r="H2" s="3">
         <v>3817</v>
       </c>
-      <c r="H2" s="3"/>
       <c r="I2" s="3"/>
-      <c r="J2" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J2" s="3"/>
+      <c r="K2" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>6917625957</v>
       </c>
@@ -2630,19 +2700,22 @@
       <c r="E3" s="3">
         <v>9431376706</v>
       </c>
-      <c r="F3" s="3">
+      <c r="F3" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="G3" s="3">
         <v>1314</v>
       </c>
-      <c r="G3" s="3">
+      <c r="H3" s="3">
         <v>3256</v>
       </c>
-      <c r="H3" s="3"/>
       <c r="I3" s="3"/>
-      <c r="J3" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J3" s="3"/>
+      <c r="K3" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>1859639165</v>
       </c>
@@ -2658,19 +2731,22 @@
       <c r="E4" s="3">
         <v>7903410549</v>
       </c>
-      <c r="F4" s="3">
+      <c r="F4" s="3" t="s">
+        <v>710</v>
+      </c>
+      <c r="G4" s="3">
         <v>1335</v>
       </c>
-      <c r="G4" s="3">
+      <c r="H4" s="3">
         <v>3099</v>
       </c>
-      <c r="H4" s="3"/>
       <c r="I4" s="3"/>
-      <c r="J4" s="3" t="s">
+      <c r="J4" s="3"/>
+      <c r="K4" s="3" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>3796226153</v>
       </c>
@@ -2686,19 +2762,22 @@
       <c r="E5" s="3">
         <v>9031946579</v>
       </c>
-      <c r="F5" s="3">
+      <c r="F5" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="G5" s="3">
         <v>825</v>
       </c>
-      <c r="G5" s="3">
+      <c r="H5" s="3">
         <v>103</v>
       </c>
-      <c r="H5" s="3"/>
       <c r="I5" s="3"/>
-      <c r="J5" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J5" s="3"/>
+      <c r="K5" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>7020129892</v>
       </c>
@@ -2714,21 +2793,24 @@
       <c r="E6" s="3">
         <v>9661123131</v>
       </c>
-      <c r="F6" s="3">
+      <c r="F6" s="3" t="s">
+        <v>711</v>
+      </c>
+      <c r="G6" s="3">
         <v>4011</v>
       </c>
-      <c r="G6" s="3">
+      <c r="H6" s="3">
         <v>3984</v>
       </c>
-      <c r="H6" s="3" t="s">
+      <c r="I6" s="3" t="s">
         <v>474</v>
       </c>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3" t="s">
+      <c r="J6" s="3"/>
+      <c r="K6" s="3" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>8297079998</v>
       </c>
@@ -2744,21 +2826,24 @@
       <c r="E7" s="3">
         <v>9835982099</v>
       </c>
-      <c r="F7" s="3">
+      <c r="F7" s="3" t="s">
+        <v>711</v>
+      </c>
+      <c r="G7" s="3">
         <v>844</v>
       </c>
-      <c r="G7" s="3">
+      <c r="H7" s="3">
         <v>3149</v>
       </c>
-      <c r="H7" s="3" t="s">
+      <c r="I7" s="3" t="s">
         <v>476</v>
       </c>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3" t="s">
+      <c r="J7" s="3"/>
+      <c r="K7" s="3" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>3109998394</v>
       </c>
@@ -2774,21 +2859,24 @@
       <c r="E8" s="3">
         <v>9430350350</v>
       </c>
-      <c r="F8" s="3">
+      <c r="F8" s="3" t="s">
+        <v>711</v>
+      </c>
+      <c r="G8" s="3">
         <v>4011</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3103</v>
       </c>
-      <c r="H8" s="3" t="s">
+      <c r="I8" s="3" t="s">
         <v>474</v>
       </c>
-      <c r="I8" s="3"/>
-      <c r="J8" s="3" t="s">
+      <c r="J8" s="3"/>
+      <c r="K8" s="3" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>7479748437</v>
       </c>
@@ -2804,19 +2892,22 @@
       <c r="E9" s="3">
         <v>7261002563</v>
       </c>
-      <c r="F9" s="3">
+      <c r="F9" s="3" t="s">
+        <v>712</v>
+      </c>
+      <c r="G9" s="3">
         <v>765</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>3106</v>
       </c>
-      <c r="H9" s="3"/>
       <c r="I9" s="3"/>
-      <c r="J9" s="3" t="s">
+      <c r="J9" s="3"/>
+      <c r="K9" s="3" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>2009738585</v>
       </c>
@@ -2832,21 +2923,24 @@
       <c r="E10" s="3">
         <v>9234703171</v>
       </c>
-      <c r="F10" s="3">
+      <c r="F10" s="3" t="s">
+        <v>711</v>
+      </c>
+      <c r="G10" s="3">
         <v>844</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>3964</v>
       </c>
-      <c r="H10" s="3" t="s">
+      <c r="I10" s="3" t="s">
         <v>479</v>
       </c>
-      <c r="I10" s="3"/>
-      <c r="J10" s="3" t="s">
+      <c r="J10" s="3"/>
+      <c r="K10" s="3" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>5585147179</v>
       </c>
@@ -2862,19 +2956,22 @@
       <c r="E11" s="3">
         <v>9631502540</v>
       </c>
-      <c r="F11" s="3">
+      <c r="F11" s="3" t="s">
+        <v>712</v>
+      </c>
+      <c r="G11" s="3">
         <v>804</v>
       </c>
-      <c r="G11" s="3">
+      <c r="H11" s="3">
         <v>3290</v>
       </c>
-      <c r="H11" s="3"/>
       <c r="I11" s="3"/>
-      <c r="J11" s="3" t="s">
+      <c r="J11" s="3"/>
+      <c r="K11" s="3" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>3968136340</v>
       </c>
@@ -2890,19 +2987,22 @@
       <c r="E12" s="3">
         <v>7033075530</v>
       </c>
-      <c r="F12" s="3">
+      <c r="F12" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="G12" s="3">
         <v>824</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>3269</v>
       </c>
-      <c r="H12" s="3"/>
       <c r="I12" s="3"/>
-      <c r="J12" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J12" s="3"/>
+      <c r="K12" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <v>3833133537</v>
       </c>
@@ -2918,19 +3018,22 @@
       <c r="E13" s="3">
         <v>9431311011</v>
       </c>
-      <c r="F13" s="3">
+      <c r="F13" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="G13" s="3">
         <v>837</v>
       </c>
-      <c r="G13" s="3">
+      <c r="H13" s="3">
         <v>3889</v>
       </c>
-      <c r="H13" s="3"/>
       <c r="I13" s="3"/>
-      <c r="J13" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J13" s="3"/>
+      <c r="K13" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
         <v>3643925307</v>
       </c>
@@ -2946,19 +3049,22 @@
       <c r="E14" s="3">
         <v>9234224920</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="3" t="s">
+        <v>708</v>
+      </c>
+      <c r="G14" s="3">
         <v>806</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>132</v>
       </c>
-      <c r="H14" s="3"/>
       <c r="I14" s="3"/>
-      <c r="J14" s="3" t="s">
+      <c r="J14" s="3"/>
+      <c r="K14" s="3" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
         <v>7230995846</v>
       </c>
@@ -2974,19 +3080,22 @@
       <c r="E15" s="3">
         <v>7061946795</v>
       </c>
-      <c r="F15" s="3">
+      <c r="F15" s="3" t="s">
+        <v>713</v>
+      </c>
+      <c r="G15" s="3">
         <v>839</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>3232</v>
       </c>
-      <c r="H15" s="3"/>
       <c r="I15" s="3"/>
-      <c r="J15" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J15" s="3"/>
+      <c r="K15" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
         <v>5611988257</v>
       </c>
@@ -3000,19 +3109,22 @@
       <c r="E16" s="3">
         <v>7909064503</v>
       </c>
-      <c r="F16" s="3">
+      <c r="F16" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="G16" s="3">
         <v>814</v>
       </c>
-      <c r="G16" s="3">
+      <c r="H16" s="3">
         <v>3173</v>
       </c>
-      <c r="H16" s="3"/>
       <c r="I16" s="3"/>
-      <c r="J16" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J16" s="3"/>
+      <c r="K16" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
         <v>1465726979</v>
       </c>
@@ -3028,21 +3140,24 @@
       <c r="E17" s="3">
         <v>8651002016</v>
       </c>
-      <c r="F17" s="3">
+      <c r="F17" s="3" t="s">
+        <v>714</v>
+      </c>
+      <c r="G17" s="3">
         <v>889</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>3868</v>
       </c>
-      <c r="H17" s="3" t="s">
+      <c r="I17" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="I17" s="3"/>
-      <c r="J17" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J17" s="3"/>
+      <c r="K17" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
         <v>1517238512</v>
       </c>
@@ -3058,19 +3173,22 @@
       <c r="E18" s="3">
         <v>9123275748</v>
       </c>
-      <c r="F18" s="3">
+      <c r="F18" s="3" t="s">
+        <v>712</v>
+      </c>
+      <c r="G18" s="3">
         <v>1357</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>3982</v>
       </c>
-      <c r="H18" s="3"/>
       <c r="I18" s="3"/>
-      <c r="J18" s="3" t="s">
+      <c r="J18" s="3"/>
+      <c r="K18" s="3" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
         <v>3552734030</v>
       </c>
@@ -3086,19 +3204,22 @@
       <c r="E19" s="3">
         <v>7370070067</v>
       </c>
-      <c r="F19" s="3">
+      <c r="F19" s="3" t="s">
+        <v>708</v>
+      </c>
+      <c r="G19" s="3">
         <v>836</v>
       </c>
-      <c r="G19" s="3">
+      <c r="H19" s="3">
         <v>3197</v>
       </c>
-      <c r="H19" s="3"/>
       <c r="I19" s="3"/>
-      <c r="J19" s="3" t="s">
+      <c r="J19" s="3"/>
+      <c r="K19" s="3" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
         <v>7451074474</v>
       </c>
@@ -3114,19 +3235,22 @@
       <c r="E20" s="3">
         <v>8434544468</v>
       </c>
-      <c r="F20" s="3">
+      <c r="F20" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="G20" s="3">
         <v>822</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>3287</v>
       </c>
-      <c r="H20" s="3"/>
       <c r="I20" s="3"/>
-      <c r="J20" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J20" s="3"/>
+      <c r="K20" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
         <v>1669467771</v>
       </c>
@@ -3142,21 +3266,24 @@
       <c r="E21" s="3">
         <v>8235278909</v>
       </c>
-      <c r="F21" s="3">
+      <c r="F21" s="3" t="s">
+        <v>711</v>
+      </c>
+      <c r="G21" s="3">
         <v>4011</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>3832</v>
       </c>
-      <c r="H21" s="3" t="s">
+      <c r="I21" s="3" t="s">
         <v>474</v>
       </c>
-      <c r="I21" s="3"/>
-      <c r="J21" s="3" t="s">
+      <c r="J21" s="3"/>
+      <c r="K21" s="3" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
         <v>9027149675</v>
       </c>
@@ -3172,19 +3299,22 @@
       <c r="E22" s="3">
         <v>9608591820</v>
       </c>
-      <c r="F22" s="3">
+      <c r="F22" s="3" t="s">
+        <v>713</v>
+      </c>
+      <c r="G22" s="3">
         <v>866</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>3179</v>
       </c>
-      <c r="H22" s="3"/>
       <c r="I22" s="3"/>
-      <c r="J22" s="3" t="s">
+      <c r="J22" s="3"/>
+      <c r="K22" s="3" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
         <v>4769993708</v>
       </c>
@@ -3200,19 +3330,22 @@
       <c r="E23" s="3">
         <v>8797828850</v>
       </c>
-      <c r="F23" s="3">
+      <c r="F23" s="3" t="s">
+        <v>710</v>
+      </c>
+      <c r="G23" s="3">
         <v>827</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>3580</v>
       </c>
-      <c r="H23" s="3"/>
       <c r="I23" s="3"/>
-      <c r="J23" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J23" s="3"/>
+      <c r="K23" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
         <v>6773172299</v>
       </c>
@@ -3228,19 +3361,22 @@
       <c r="E24" s="3">
         <v>8935913061</v>
       </c>
-      <c r="F24" s="3">
+      <c r="F24" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="G24" s="3">
         <v>1221</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>3365</v>
       </c>
-      <c r="H24" s="3"/>
       <c r="I24" s="3"/>
-      <c r="J24" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J24" s="3"/>
+      <c r="K24" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
         <v>6681843167</v>
       </c>
@@ -3256,19 +3392,22 @@
       <c r="E25" s="3">
         <v>6397215387</v>
       </c>
-      <c r="F25" s="3">
+      <c r="F25" s="3" t="s">
+        <v>715</v>
+      </c>
+      <c r="G25" s="3">
         <v>894</v>
       </c>
-      <c r="G25" s="3">
+      <c r="H25" s="3">
         <v>3115</v>
       </c>
-      <c r="H25" s="3"/>
       <c r="I25" s="3"/>
-      <c r="J25" s="3" t="s">
+      <c r="J25" s="3"/>
+      <c r="K25" s="3" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="3">
         <v>1524539357</v>
       </c>
@@ -3284,19 +3423,22 @@
       <c r="E26" s="3">
         <v>9708557316</v>
       </c>
-      <c r="F26" s="3">
+      <c r="F26" s="3" t="s">
+        <v>716</v>
+      </c>
+      <c r="G26" s="3">
         <v>825</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>3165</v>
       </c>
-      <c r="H26" s="3"/>
       <c r="I26" s="3"/>
-      <c r="J26" s="3" t="s">
+      <c r="J26" s="3"/>
+      <c r="K26" s="3" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="3">
         <v>7039937781</v>
       </c>
@@ -3312,19 +3454,22 @@
       <c r="E27" s="3">
         <v>9123194625</v>
       </c>
-      <c r="F27" s="3">
+      <c r="F27" s="3" t="s">
+        <v>715</v>
+      </c>
+      <c r="G27" s="3">
         <v>892</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>3118</v>
       </c>
-      <c r="H27" s="3"/>
       <c r="I27" s="3"/>
-      <c r="J27" s="3" t="s">
+      <c r="J27" s="3"/>
+      <c r="K27" s="3" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="3">
         <v>4222361504</v>
       </c>
@@ -3340,19 +3485,22 @@
       <c r="E28" s="3">
         <v>9939862184</v>
       </c>
-      <c r="F28" s="3">
+      <c r="F28" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="G28" s="3">
         <v>856</v>
       </c>
-      <c r="G28" s="3">
+      <c r="H28" s="3">
         <v>3898</v>
       </c>
-      <c r="H28" s="3"/>
       <c r="I28" s="3"/>
-      <c r="J28" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J28" s="3"/>
+      <c r="K28" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="3">
         <v>7403854611</v>
       </c>
@@ -3366,19 +3514,22 @@
       <c r="E29" s="3">
         <v>7739340434</v>
       </c>
-      <c r="F29" s="3">
+      <c r="F29" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="G29" s="3">
         <v>823</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>3341</v>
       </c>
-      <c r="H29" s="3"/>
       <c r="I29" s="3"/>
-      <c r="J29" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J29" s="3"/>
+      <c r="K29" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="3">
         <v>4015968403</v>
       </c>
@@ -3394,19 +3545,22 @@
       <c r="E30" s="3">
         <v>9110926596</v>
       </c>
-      <c r="F30" s="3">
+      <c r="F30" s="3" t="s">
+        <v>717</v>
+      </c>
+      <c r="G30" s="3">
         <v>876</v>
       </c>
-      <c r="G30" s="3">
+      <c r="H30" s="3">
         <v>3266</v>
       </c>
-      <c r="H30" s="3"/>
       <c r="I30" s="3"/>
-      <c r="J30" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J30" s="3"/>
+      <c r="K30" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="3">
         <v>8288130097</v>
       </c>
@@ -3420,19 +3574,22 @@
       <c r="E31" s="3">
         <v>8709827275</v>
       </c>
-      <c r="F31" s="3">
+      <c r="F31" s="3" t="s">
+        <v>710</v>
+      </c>
+      <c r="G31" s="3">
         <v>1300</v>
       </c>
-      <c r="G31" s="3">
+      <c r="H31" s="3">
         <v>3123</v>
       </c>
-      <c r="H31" s="3"/>
       <c r="I31" s="3"/>
-      <c r="J31" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J31" s="3"/>
+      <c r="K31" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="3">
         <v>8915040349</v>
       </c>
@@ -3448,19 +3605,22 @@
       <c r="E32" s="3">
         <v>9931089953</v>
       </c>
-      <c r="F32" s="3">
+      <c r="F32" s="3" t="s">
+        <v>718</v>
+      </c>
+      <c r="G32" s="3">
         <v>860</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>3390</v>
       </c>
-      <c r="H32" s="3"/>
       <c r="I32" s="3"/>
-      <c r="J32" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J32" s="3"/>
+      <c r="K32" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="3">
         <v>5345996909</v>
       </c>
@@ -3476,19 +3636,22 @@
       <c r="E33" s="3">
         <v>9973830270</v>
       </c>
-      <c r="F33" s="3">
+      <c r="F33" s="3" t="s">
+        <v>708</v>
+      </c>
+      <c r="G33" s="3">
         <v>1297</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>3233</v>
       </c>
-      <c r="H33" s="3"/>
       <c r="I33" s="3"/>
-      <c r="J33" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J33" s="3"/>
+      <c r="K33" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" s="3">
         <v>8202192895</v>
       </c>
@@ -3504,19 +3667,22 @@
       <c r="E34" s="3">
         <v>9507150233</v>
       </c>
-      <c r="F34" s="3">
+      <c r="F34" s="3" t="s">
+        <v>708</v>
+      </c>
+      <c r="G34" s="3">
         <v>1297</v>
       </c>
-      <c r="G34" s="3">
+      <c r="H34" s="3">
         <v>3131</v>
       </c>
-      <c r="H34" s="3"/>
       <c r="I34" s="3"/>
-      <c r="J34" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J34" s="3"/>
+      <c r="K34" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" s="3">
         <v>7701911603</v>
       </c>
@@ -3532,19 +3698,22 @@
       <c r="E35" s="3">
         <v>8384021596</v>
       </c>
-      <c r="F35" s="3">
+      <c r="F35" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="G35" s="3">
         <v>856</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>3130</v>
       </c>
-      <c r="H35" s="3"/>
       <c r="I35" s="3"/>
-      <c r="J35" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J35" s="3"/>
+      <c r="K35" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" s="3">
         <v>5340497735</v>
       </c>
@@ -3560,19 +3729,22 @@
       <c r="E36" s="3">
         <v>9608210185</v>
       </c>
-      <c r="F36" s="3">
+      <c r="F36" s="3" t="s">
+        <v>713</v>
+      </c>
+      <c r="G36" s="3">
         <v>866</v>
       </c>
-      <c r="G36" s="3">
+      <c r="H36" s="3">
         <v>3126</v>
       </c>
-      <c r="H36" s="3"/>
       <c r="I36" s="3"/>
-      <c r="J36" s="3" t="s">
+      <c r="J36" s="3"/>
+      <c r="K36" s="3" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" s="3">
         <v>4627553372</v>
       </c>
@@ -3588,19 +3760,22 @@
       <c r="E37" s="3">
         <v>9835930215</v>
       </c>
-      <c r="F37" s="3">
+      <c r="F37" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="G37" s="3">
         <v>826</v>
       </c>
-      <c r="G37" s="3">
+      <c r="H37" s="3">
         <v>3936</v>
       </c>
-      <c r="H37" s="3"/>
       <c r="I37" s="3"/>
-      <c r="J37" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J37" s="3"/>
+      <c r="K37" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" s="3">
         <v>1206150772</v>
       </c>
@@ -3616,19 +3791,22 @@
       <c r="E38" s="3">
         <v>9905121910</v>
       </c>
-      <c r="F38" s="3">
+      <c r="F38" s="3" t="s">
+        <v>717</v>
+      </c>
+      <c r="G38" s="3">
         <v>837</v>
       </c>
-      <c r="G38" s="3">
+      <c r="H38" s="3">
         <v>3129</v>
       </c>
-      <c r="H38" s="3"/>
       <c r="I38" s="3"/>
-      <c r="J38" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J38" s="3"/>
+      <c r="K38" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" s="3">
         <v>3768733861</v>
       </c>
@@ -3644,21 +3822,24 @@
       <c r="E39" s="3">
         <v>9279279633</v>
       </c>
-      <c r="F39" s="3">
+      <c r="F39" s="3" t="s">
+        <v>711</v>
+      </c>
+      <c r="G39" s="3">
         <v>844</v>
       </c>
-      <c r="G39" s="3">
+      <c r="H39" s="3">
         <v>3963</v>
       </c>
-      <c r="H39" s="3" t="s">
+      <c r="I39" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="I39" s="3"/>
-      <c r="J39" s="3" t="s">
+      <c r="J39" s="3"/>
+      <c r="K39" s="3" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" s="3">
         <v>5594680250</v>
       </c>
@@ -3674,21 +3855,24 @@
       <c r="E40" s="3">
         <v>9934354608</v>
       </c>
-      <c r="F40" s="3">
+      <c r="F40" s="3" t="s">
+        <v>711</v>
+      </c>
+      <c r="G40" s="3">
         <v>890</v>
       </c>
-      <c r="G40" s="3">
+      <c r="H40" s="3">
         <v>3901</v>
       </c>
-      <c r="H40" s="3" t="s">
+      <c r="I40" s="3" t="s">
         <v>486</v>
       </c>
-      <c r="I40" s="3"/>
-      <c r="J40" s="3" t="s">
+      <c r="J40" s="3"/>
+      <c r="K40" s="3" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" s="3">
         <v>6845830570</v>
       </c>
@@ -3704,19 +3888,22 @@
       <c r="E41" s="3">
         <v>9955599125</v>
       </c>
-      <c r="F41" s="3">
+      <c r="F41" s="3" t="s">
+        <v>708</v>
+      </c>
+      <c r="G41" s="3">
         <v>806</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>132</v>
       </c>
-      <c r="H41" s="3"/>
       <c r="I41" s="3"/>
-      <c r="J41" s="3" t="s">
+      <c r="J41" s="3"/>
+      <c r="K41" s="3" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" s="3">
         <v>3913334537</v>
       </c>
@@ -3732,19 +3919,22 @@
       <c r="E42" s="3">
         <v>9905330091</v>
       </c>
-      <c r="F42" s="3">
+      <c r="F42" s="3" t="s">
+        <v>713</v>
+      </c>
+      <c r="G42" s="3">
         <v>1303</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>3931</v>
       </c>
-      <c r="H42" s="3"/>
       <c r="I42" s="3"/>
-      <c r="J42" s="3" t="s">
+      <c r="J42" s="3"/>
+      <c r="K42" s="3" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" s="3">
         <v>6669858999</v>
       </c>
@@ -3760,19 +3950,22 @@
       <c r="E43" s="3">
         <v>9386158889</v>
       </c>
-      <c r="F43" s="3">
+      <c r="F43" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="G43" s="3">
         <v>841</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2937</v>
       </c>
-      <c r="H43" s="3"/>
       <c r="I43" s="3"/>
-      <c r="J43" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J43" s="3"/>
+      <c r="K43" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" s="3">
         <v>3332842006</v>
       </c>
@@ -3788,19 +3981,22 @@
       <c r="E44" s="3">
         <v>9996130478</v>
       </c>
-      <c r="F44" s="3">
+      <c r="F44" s="3" t="s">
+        <v>712</v>
+      </c>
+      <c r="G44" s="3">
         <v>765</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>3154</v>
       </c>
-      <c r="H44" s="3"/>
       <c r="I44" s="3"/>
-      <c r="J44" s="3" t="s">
+      <c r="J44" s="3"/>
+      <c r="K44" s="3" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" s="3">
         <v>5380942201</v>
       </c>
@@ -3814,19 +4010,22 @@
       <c r="E45" s="3">
         <v>8210756126</v>
       </c>
-      <c r="F45" s="3">
+      <c r="F45" s="3" t="s">
+        <v>716</v>
+      </c>
+      <c r="G45" s="3">
         <v>825</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>3200</v>
       </c>
-      <c r="H45" s="3"/>
       <c r="I45" s="3"/>
-      <c r="J45" s="3" t="s">
+      <c r="J45" s="3"/>
+      <c r="K45" s="3" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" s="3">
         <v>8309797193</v>
       </c>
@@ -3842,19 +4041,22 @@
       <c r="E46" s="3">
         <v>9073775196</v>
       </c>
-      <c r="F46" s="3">
+      <c r="F46" s="3" t="s">
+        <v>719</v>
+      </c>
+      <c r="G46" s="3">
         <v>656</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>201</v>
       </c>
-      <c r="H46" s="3"/>
       <c r="I46" s="3"/>
-      <c r="J46" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J46" s="3"/>
+      <c r="K46" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" s="3">
         <v>8683445897</v>
       </c>
@@ -3870,19 +4072,22 @@
       <c r="E47" s="3">
         <v>8877046844</v>
       </c>
-      <c r="F47" s="3">
+      <c r="F47" s="3" t="s">
+        <v>712</v>
+      </c>
+      <c r="G47" s="3">
         <v>765</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>3230</v>
       </c>
-      <c r="H47" s="3"/>
       <c r="I47" s="3"/>
-      <c r="J47" s="3" t="s">
+      <c r="J47" s="3"/>
+      <c r="K47" s="3" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" s="3">
         <v>5396792463</v>
       </c>
@@ -3896,19 +4101,22 @@
       <c r="E48" s="3">
         <v>9835177850</v>
       </c>
-      <c r="F48" s="3">
+      <c r="F48" s="3" t="s">
+        <v>713</v>
+      </c>
+      <c r="G48" s="3">
         <v>882</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3234</v>
       </c>
-      <c r="H48" s="3"/>
       <c r="I48" s="3"/>
-      <c r="J48" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J48" s="3"/>
+      <c r="K48" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" s="3">
         <v>3675751664</v>
       </c>
@@ -3922,19 +4130,22 @@
       <c r="E49" s="3">
         <v>8789927358</v>
       </c>
-      <c r="F49" s="3">
+      <c r="F49" s="3" t="s">
+        <v>713</v>
+      </c>
+      <c r="G49" s="3">
         <v>1303</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>3145</v>
       </c>
-      <c r="H49" s="3"/>
       <c r="I49" s="3"/>
-      <c r="J49" s="3" t="s">
+      <c r="J49" s="3"/>
+      <c r="K49" s="3" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" s="3">
         <v>3423963007</v>
       </c>
@@ -3950,19 +4161,22 @@
       <c r="E50" s="3">
         <v>9431552726</v>
       </c>
-      <c r="F50" s="3">
+      <c r="F50" s="3" t="s">
+        <v>708</v>
+      </c>
+      <c r="G50" s="3">
         <v>878</v>
       </c>
-      <c r="G50" s="3">
+      <c r="H50" s="3">
         <v>3144</v>
       </c>
-      <c r="H50" s="3"/>
       <c r="I50" s="3"/>
-      <c r="J50" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J50" s="3"/>
+      <c r="K50" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" s="3">
         <v>6666517538</v>
       </c>
@@ -3978,19 +4192,22 @@
       <c r="E51" s="3">
         <v>7004451454</v>
       </c>
-      <c r="F51" s="3">
+      <c r="F51" s="3" t="s">
+        <v>715</v>
+      </c>
+      <c r="G51" s="3">
         <v>805</v>
       </c>
-      <c r="G51" s="3">
+      <c r="H51" s="3">
         <v>3848</v>
       </c>
-      <c r="H51" s="3"/>
       <c r="I51" s="3"/>
-      <c r="J51" s="3" t="s">
+      <c r="J51" s="3"/>
+      <c r="K51" s="3" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" s="3">
         <v>2537795461</v>
       </c>
@@ -4006,19 +4223,22 @@
       <c r="E52" s="3">
         <v>8789505553</v>
       </c>
-      <c r="F52" s="3">
+      <c r="F52" s="3" t="s">
+        <v>712</v>
+      </c>
+      <c r="G52" s="3">
         <v>804</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>3837</v>
       </c>
-      <c r="H52" s="3"/>
       <c r="I52" s="3"/>
-      <c r="J52" s="3" t="s">
+      <c r="J52" s="3"/>
+      <c r="K52" s="3" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" s="3">
         <v>6369649510</v>
       </c>
@@ -4034,19 +4254,22 @@
       <c r="E53" s="3">
         <v>7070093334</v>
       </c>
-      <c r="F53" s="3">
+      <c r="F53" s="3" t="s">
+        <v>713</v>
+      </c>
+      <c r="G53" s="3">
         <v>882</v>
       </c>
-      <c r="G53" s="3">
+      <c r="H53" s="3">
         <v>116</v>
       </c>
-      <c r="H53" s="3"/>
       <c r="I53" s="3"/>
-      <c r="J53" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J53" s="3"/>
+      <c r="K53" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" s="3">
         <v>3990514466</v>
       </c>
@@ -4062,19 +4285,22 @@
       <c r="E54" s="3">
         <v>9608759216</v>
       </c>
-      <c r="F54" s="3">
+      <c r="F54" s="3" t="s">
+        <v>713</v>
+      </c>
+      <c r="G54" s="3">
         <v>882</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>3151</v>
       </c>
-      <c r="H54" s="3"/>
       <c r="I54" s="3"/>
-      <c r="J54" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J54" s="3"/>
+      <c r="K54" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" s="3">
         <v>2462666533</v>
       </c>
@@ -4090,19 +4316,22 @@
       <c r="E55" s="3">
         <v>9955363623</v>
       </c>
-      <c r="F55" s="3">
+      <c r="F55" s="3" t="s">
+        <v>713</v>
+      </c>
+      <c r="G55" s="3">
         <v>882</v>
       </c>
-      <c r="G55" s="3">
+      <c r="H55" s="3">
         <v>3152</v>
       </c>
-      <c r="H55" s="3"/>
       <c r="I55" s="3"/>
-      <c r="J55" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J55" s="3"/>
+      <c r="K55" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" s="3">
         <v>3405422707</v>
       </c>
@@ -4118,19 +4347,22 @@
       <c r="E56" s="3">
         <v>9304211966</v>
       </c>
-      <c r="F56" s="3">
+      <c r="F56" s="3" t="s">
+        <v>713</v>
+      </c>
+      <c r="G56" s="3">
         <v>870</v>
       </c>
-      <c r="G56" s="3">
+      <c r="H56" s="3">
         <v>3161</v>
       </c>
-      <c r="H56" s="3"/>
       <c r="I56" s="3"/>
-      <c r="J56" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J56" s="3"/>
+      <c r="K56" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" s="3">
         <v>1121263937</v>
       </c>
@@ -4144,19 +4376,22 @@
       <c r="E57" s="3">
         <v>7209782844</v>
       </c>
-      <c r="F57" s="3">
+      <c r="F57" s="3" t="s">
+        <v>713</v>
+      </c>
+      <c r="G57" s="3">
         <v>870</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3979</v>
       </c>
-      <c r="H57" s="3"/>
       <c r="I57" s="3"/>
-      <c r="J57" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J57" s="3"/>
+      <c r="K57" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" s="3">
         <v>5909201840</v>
       </c>
@@ -4172,19 +4407,22 @@
       <c r="E58" s="3">
         <v>8825116361</v>
       </c>
-      <c r="F58" s="3">
+      <c r="F58" s="3" t="s">
+        <v>719</v>
+      </c>
+      <c r="G58" s="3">
         <v>656</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>202</v>
       </c>
-      <c r="H58" s="3"/>
       <c r="I58" s="3"/>
-      <c r="J58" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J58" s="3"/>
+      <c r="K58" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" s="3">
         <v>2221835971</v>
       </c>
@@ -4200,19 +4438,22 @@
       <c r="E59" s="3">
         <v>9031313032</v>
       </c>
-      <c r="F59" s="3">
+      <c r="F59" s="3" t="s">
+        <v>713</v>
+      </c>
+      <c r="G59" s="3">
         <v>1303</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>3217</v>
       </c>
-      <c r="H59" s="3"/>
       <c r="I59" s="3"/>
-      <c r="J59" s="3" t="s">
+      <c r="J59" s="3"/>
+      <c r="K59" s="3" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" s="3">
         <v>3460482331</v>
       </c>
@@ -4228,19 +4469,22 @@
       <c r="E60" s="3">
         <v>9431971709</v>
       </c>
-      <c r="F60" s="3">
+      <c r="F60" s="3" t="s">
+        <v>720</v>
+      </c>
+      <c r="G60" s="3">
         <v>1284</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>3163</v>
       </c>
-      <c r="H60" s="3"/>
       <c r="I60" s="3"/>
-      <c r="J60" s="3" t="s">
+      <c r="J60" s="3"/>
+      <c r="K60" s="3" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" s="3">
         <v>2952499748</v>
       </c>
@@ -4254,19 +4498,22 @@
       <c r="E61" s="3">
         <v>9123152130</v>
       </c>
-      <c r="F61" s="3">
+      <c r="F61" s="3" t="s">
+        <v>719</v>
+      </c>
+      <c r="G61" s="3">
         <v>817</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>3262</v>
       </c>
-      <c r="H61" s="3"/>
       <c r="I61" s="3"/>
-      <c r="J61" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J61" s="3"/>
+      <c r="K61" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" s="3">
         <v>8932426014</v>
       </c>
@@ -4282,19 +4529,22 @@
       <c r="E62" s="3">
         <v>9431297531</v>
       </c>
-      <c r="F62" s="3">
+      <c r="F62" s="3" t="s">
+        <v>721</v>
+      </c>
+      <c r="G62" s="3">
         <v>871</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>3231</v>
       </c>
-      <c r="H62" s="3"/>
       <c r="I62" s="3"/>
-      <c r="J62" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J62" s="3"/>
+      <c r="K62" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" s="3">
         <v>9054357395</v>
       </c>
@@ -4308,19 +4558,22 @@
       <c r="E63" s="3">
         <v>9931767021</v>
       </c>
-      <c r="F63" s="3">
+      <c r="F63" s="3" t="s">
+        <v>712</v>
+      </c>
+      <c r="G63" s="3">
         <v>765</v>
       </c>
-      <c r="G63" s="3">
+      <c r="H63" s="3">
         <v>3228</v>
       </c>
-      <c r="H63" s="3"/>
       <c r="I63" s="3"/>
-      <c r="J63" s="3" t="s">
+      <c r="J63" s="3"/>
+      <c r="K63" s="3" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" s="3">
         <v>3160865300</v>
       </c>
@@ -4336,19 +4589,22 @@
       <c r="E64" s="3">
         <v>7542920732</v>
       </c>
-      <c r="F64" s="3">
+      <c r="F64" s="3" t="s">
+        <v>712</v>
+      </c>
+      <c r="G64" s="3">
         <v>765</v>
       </c>
-      <c r="G64" s="3">
+      <c r="H64" s="3">
         <v>3230</v>
       </c>
-      <c r="H64" s="3"/>
       <c r="I64" s="3"/>
-      <c r="J64" s="3" t="s">
+      <c r="J64" s="3"/>
+      <c r="K64" s="3" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" s="3">
         <v>7331127189</v>
       </c>
@@ -4364,19 +4620,22 @@
       <c r="E65" s="3">
         <v>8709872542</v>
       </c>
-      <c r="F65" s="3">
+      <c r="F65" s="3" t="s">
+        <v>713</v>
+      </c>
+      <c r="G65" s="3">
         <v>1303</v>
       </c>
-      <c r="G65" s="3">
+      <c r="H65" s="3">
         <v>3869</v>
       </c>
-      <c r="H65" s="3"/>
       <c r="I65" s="3"/>
-      <c r="J65" s="3" t="s">
+      <c r="J65" s="3"/>
+      <c r="K65" s="3" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" s="3">
         <v>6861139517</v>
       </c>
@@ -4392,19 +4651,22 @@
       <c r="E66" s="3">
         <v>8709270950</v>
       </c>
-      <c r="F66" s="3">
+      <c r="F66" s="3" t="s">
+        <v>717</v>
+      </c>
+      <c r="G66" s="3">
         <v>836</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3197</v>
       </c>
-      <c r="H66" s="3"/>
       <c r="I66" s="3"/>
-      <c r="J66" s="3" t="s">
+      <c r="J66" s="3"/>
+      <c r="K66" s="3" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" s="3">
         <v>3801997259</v>
       </c>
@@ -4420,19 +4682,22 @@
       <c r="E67" s="3">
         <v>7481024818</v>
       </c>
-      <c r="F67" s="3">
+      <c r="F67" s="3" t="s">
+        <v>713</v>
+      </c>
+      <c r="G67" s="3">
         <v>843</v>
       </c>
-      <c r="G67" s="3">
+      <c r="H67" s="3">
         <v>3224</v>
       </c>
-      <c r="H67" s="3"/>
       <c r="I67" s="3"/>
-      <c r="J67" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J67" s="3"/>
+      <c r="K67" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" s="3">
         <v>4144165211</v>
       </c>
@@ -4448,19 +4713,22 @@
       <c r="E68" s="3">
         <v>9430300409</v>
       </c>
-      <c r="F68" s="3">
+      <c r="F68" s="3" t="s">
+        <v>708</v>
+      </c>
+      <c r="G68" s="3">
         <v>847</v>
       </c>
-      <c r="G68" s="3">
+      <c r="H68" s="3">
         <v>3212</v>
       </c>
-      <c r="H68" s="3"/>
       <c r="I68" s="3"/>
-      <c r="J68" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J68" s="3"/>
+      <c r="K68" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" s="3">
         <v>7724015493</v>
       </c>
@@ -4476,19 +4744,22 @@
       <c r="E69" s="3">
         <v>8092869255</v>
       </c>
-      <c r="F69" s="3">
+      <c r="F69" s="3" t="s">
+        <v>720</v>
+      </c>
+      <c r="G69" s="3">
         <v>1284</v>
       </c>
-      <c r="G69" s="3">
+      <c r="H69" s="3">
         <v>3208</v>
       </c>
-      <c r="H69" s="3"/>
       <c r="I69" s="3"/>
-      <c r="J69" s="3" t="s">
+      <c r="J69" s="3"/>
+      <c r="K69" s="3" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" s="3">
         <v>1862461218</v>
       </c>
@@ -4504,19 +4775,22 @@
       <c r="E70" s="3">
         <v>9832922501</v>
       </c>
-      <c r="F70" s="3">
+      <c r="F70" s="3" t="s">
+        <v>712</v>
+      </c>
+      <c r="G70" s="3">
         <v>1238</v>
       </c>
-      <c r="G70" s="3">
+      <c r="H70" s="3">
         <v>3248</v>
       </c>
-      <c r="H70" s="3"/>
       <c r="I70" s="3"/>
-      <c r="J70" s="3" t="s">
+      <c r="J70" s="3"/>
+      <c r="K70" s="3" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" s="3">
         <v>1247399268</v>
       </c>
@@ -4532,19 +4806,22 @@
       <c r="E71" s="3">
         <v>8789047661</v>
       </c>
-      <c r="F71" s="3">
+      <c r="F71" s="3" t="s">
+        <v>722</v>
+      </c>
+      <c r="G71" s="3">
         <v>867</v>
       </c>
-      <c r="G71" s="3">
+      <c r="H71" s="3">
         <v>3210</v>
       </c>
-      <c r="H71" s="3"/>
       <c r="I71" s="3"/>
-      <c r="J71" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J71" s="3"/>
+      <c r="K71" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" s="3">
         <v>8727464701</v>
       </c>
@@ -4560,21 +4837,24 @@
       <c r="E72" s="3">
         <v>9142397454</v>
       </c>
-      <c r="F72" s="3">
+      <c r="F72" s="3" t="s">
+        <v>714</v>
+      </c>
+      <c r="G72" s="3">
         <v>886</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>3189</v>
       </c>
-      <c r="H72" s="3" t="s">
+      <c r="I72" s="3" t="s">
         <v>488</v>
       </c>
-      <c r="I72" s="3"/>
-      <c r="J72" s="3" t="s">
+      <c r="J72" s="3"/>
+      <c r="K72" s="3" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" s="3">
         <v>2638563833</v>
       </c>
@@ -4590,19 +4870,22 @@
       <c r="E73" s="3">
         <v>7004457309</v>
       </c>
-      <c r="F73" s="3">
+      <c r="F73" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="G73" s="3">
         <v>826</v>
       </c>
-      <c r="G73" s="3">
+      <c r="H73" s="3">
         <v>3198</v>
       </c>
-      <c r="H73" s="3"/>
       <c r="I73" s="3"/>
-      <c r="J73" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J73" s="3"/>
+      <c r="K73" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" s="3">
         <v>3588658820</v>
       </c>
@@ -4618,19 +4901,22 @@
       <c r="E74" s="3">
         <v>7808959782</v>
       </c>
-      <c r="F74" s="3">
+      <c r="F74" s="3" t="s">
+        <v>713</v>
+      </c>
+      <c r="G74" s="3">
         <v>882</v>
       </c>
-      <c r="G74" s="3">
+      <c r="H74" s="3">
         <v>3872</v>
       </c>
-      <c r="H74" s="3"/>
       <c r="I74" s="3"/>
-      <c r="J74" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J74" s="3"/>
+      <c r="K74" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" s="3">
         <v>3716294237</v>
       </c>
@@ -4646,19 +4932,22 @@
       <c r="E75" s="3">
         <v>8986865449</v>
       </c>
-      <c r="F75" s="3">
+      <c r="F75" s="3" t="s">
+        <v>708</v>
+      </c>
+      <c r="G75" s="3">
         <v>878</v>
       </c>
-      <c r="G75" s="3">
+      <c r="H75" s="3">
         <v>3267</v>
       </c>
-      <c r="H75" s="3"/>
       <c r="I75" s="3"/>
-      <c r="J75" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J75" s="3"/>
+      <c r="K75" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" s="3">
         <v>1840251248</v>
       </c>
@@ -4672,19 +4961,22 @@
       <c r="E76" s="3">
         <v>8294034149</v>
       </c>
-      <c r="F76" s="3">
+      <c r="F76" s="3" t="s">
+        <v>712</v>
+      </c>
+      <c r="G76" s="3">
         <v>1249</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>3171</v>
       </c>
-      <c r="H76" s="3"/>
       <c r="I76" s="3"/>
-      <c r="J76" s="3" t="s">
+      <c r="J76" s="3"/>
+      <c r="K76" s="3" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" s="3">
         <v>6002720782</v>
       </c>
@@ -4700,19 +4992,22 @@
       <c r="E77" s="3">
         <v>9835161443</v>
       </c>
-      <c r="F77" s="3">
+      <c r="F77" s="3" t="s">
+        <v>713</v>
+      </c>
+      <c r="G77" s="3">
         <v>1303</v>
       </c>
-      <c r="G77" s="3">
+      <c r="H77" s="3">
         <v>3166</v>
       </c>
-      <c r="H77" s="3"/>
       <c r="I77" s="3"/>
-      <c r="J77" s="3" t="s">
+      <c r="J77" s="3"/>
+      <c r="K77" s="3" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" s="3">
         <v>1678820666</v>
       </c>
@@ -4728,19 +5023,22 @@
       <c r="E78" s="3">
         <v>7004040787</v>
       </c>
-      <c r="F78" s="3">
+      <c r="F78" s="3" t="s">
+        <v>722</v>
+      </c>
+      <c r="G78" s="3">
         <v>877</v>
       </c>
-      <c r="G78" s="3">
+      <c r="H78" s="3">
         <v>3176</v>
       </c>
-      <c r="H78" s="3"/>
       <c r="I78" s="3"/>
-      <c r="J78" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J78" s="3"/>
+      <c r="K78" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" s="3">
         <v>7287898259</v>
       </c>
@@ -4756,19 +5054,22 @@
       <c r="E79" s="3">
         <v>7209643652</v>
       </c>
-      <c r="F79" s="3">
+      <c r="F79" s="3" t="s">
+        <v>723</v>
+      </c>
+      <c r="G79" s="3">
         <v>596</v>
       </c>
-      <c r="G79" s="3">
+      <c r="H79" s="3">
         <v>3823</v>
       </c>
-      <c r="H79" s="3"/>
       <c r="I79" s="3"/>
-      <c r="J79" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J79" s="3"/>
+      <c r="K79" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" s="3">
         <v>7065715198</v>
       </c>
@@ -4784,19 +5085,22 @@
       <c r="E80" s="3">
         <v>9304932731</v>
       </c>
-      <c r="F80" s="3">
+      <c r="F80" s="3" t="s">
+        <v>720</v>
+      </c>
+      <c r="G80" s="3">
         <v>1284</v>
       </c>
-      <c r="G80" s="3">
+      <c r="H80" s="3">
         <v>3181</v>
       </c>
-      <c r="H80" s="3"/>
       <c r="I80" s="3"/>
-      <c r="J80" s="3" t="s">
+      <c r="J80" s="3"/>
+      <c r="K80" s="3" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" s="3">
         <v>6335045168</v>
       </c>
@@ -4812,21 +5116,24 @@
       <c r="E81" s="3">
         <v>6207777925</v>
       </c>
-      <c r="F81" s="3">
+      <c r="F81" s="3" t="s">
+        <v>724</v>
+      </c>
+      <c r="G81" s="3">
         <v>885</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>3167</v>
       </c>
-      <c r="H81" s="3" t="s">
+      <c r="I81" s="3" t="s">
         <v>490</v>
       </c>
-      <c r="I81" s="3"/>
-      <c r="J81" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J81" s="3"/>
+      <c r="K81" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" s="3">
         <v>7689886031</v>
       </c>
@@ -4840,19 +5147,22 @@
       <c r="E82" s="3">
         <v>9122784236</v>
       </c>
-      <c r="F82" s="3">
+      <c r="F82" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="G82" s="3">
         <v>1221</v>
       </c>
-      <c r="G82" s="3">
+      <c r="H82" s="3">
         <v>3845</v>
       </c>
-      <c r="H82" s="3"/>
       <c r="I82" s="3"/>
-      <c r="J82" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J82" s="3"/>
+      <c r="K82" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" s="3">
         <v>4936533775</v>
       </c>
@@ -4868,19 +5178,22 @@
       <c r="E83" s="3">
         <v>9931178084</v>
       </c>
-      <c r="F83" s="3">
+      <c r="F83" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="G83" s="3">
         <v>1221</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>3193</v>
       </c>
-      <c r="H83" s="3"/>
       <c r="I83" s="3"/>
-      <c r="J83" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J83" s="3"/>
+      <c r="K83" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" s="3">
         <v>4739759407</v>
       </c>
@@ -4894,19 +5207,22 @@
       <c r="E84" s="3">
         <v>9470506249</v>
       </c>
-      <c r="F84" s="3">
+      <c r="F84" s="3" t="s">
+        <v>721</v>
+      </c>
+      <c r="G84" s="3">
         <v>871</v>
       </c>
-      <c r="G84" s="3">
+      <c r="H84" s="3">
         <v>3175</v>
       </c>
-      <c r="H84" s="3"/>
       <c r="I84" s="3"/>
-      <c r="J84" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J84" s="3"/>
+      <c r="K84" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A85" s="3">
         <v>4465648849</v>
       </c>
@@ -4922,19 +5238,22 @@
       <c r="E85" s="3">
         <v>9031071171</v>
       </c>
-      <c r="F85" s="3">
+      <c r="F85" s="3" t="s">
+        <v>713</v>
+      </c>
+      <c r="G85" s="3">
         <v>1303</v>
       </c>
-      <c r="G85" s="3">
+      <c r="H85" s="3">
         <v>3897</v>
       </c>
-      <c r="H85" s="3"/>
       <c r="I85" s="3"/>
-      <c r="J85" s="3" t="s">
+      <c r="J85" s="3"/>
+      <c r="K85" s="3" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A86" s="3">
         <v>2095245686</v>
       </c>
@@ -4950,19 +5269,22 @@
       <c r="E86" s="3">
         <v>6202363783</v>
       </c>
-      <c r="F86" s="3">
+      <c r="F86" s="3" t="s">
+        <v>725</v>
+      </c>
+      <c r="G86" s="3">
         <v>871</v>
       </c>
-      <c r="G86" s="3">
+      <c r="H86" s="3">
         <v>3260</v>
       </c>
-      <c r="H86" s="3"/>
       <c r="I86" s="3"/>
-      <c r="J86" s="3" t="s">
+      <c r="J86" s="3"/>
+      <c r="K86" s="3" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A87" s="3">
         <v>3447680219</v>
       </c>
@@ -4978,19 +5300,22 @@
       <c r="E87" s="3">
         <v>9204057773</v>
       </c>
-      <c r="F87" s="3">
+      <c r="F87" s="3" t="s">
+        <v>717</v>
+      </c>
+      <c r="G87" s="3">
         <v>874</v>
       </c>
-      <c r="G87" s="3">
+      <c r="H87" s="3">
         <v>3288</v>
       </c>
-      <c r="H87" s="3"/>
       <c r="I87" s="3"/>
-      <c r="J87" s="3" t="s">
+      <c r="J87" s="3"/>
+      <c r="K87" s="3" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A88" s="3">
         <v>2194387274</v>
       </c>
@@ -5006,19 +5331,22 @@
       <c r="E88" s="3">
         <v>9204639639</v>
       </c>
-      <c r="F88" s="3">
+      <c r="F88" s="3" t="s">
+        <v>717</v>
+      </c>
+      <c r="G88" s="3">
         <v>874</v>
       </c>
-      <c r="G88" s="3">
+      <c r="H88" s="3">
         <v>3803</v>
       </c>
-      <c r="H88" s="3"/>
       <c r="I88" s="3"/>
-      <c r="J88" s="3" t="s">
+      <c r="J88" s="3"/>
+      <c r="K88" s="3" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A89" s="3">
         <v>3687534280</v>
       </c>
@@ -5034,21 +5362,24 @@
       <c r="E89" s="3">
         <v>9234903988</v>
       </c>
-      <c r="F89" s="3">
+      <c r="F89" s="3" t="s">
+        <v>711</v>
+      </c>
+      <c r="G89" s="3">
         <v>890</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>3801</v>
       </c>
-      <c r="H89" s="3" t="s">
+      <c r="I89" s="3" t="s">
         <v>492</v>
       </c>
-      <c r="I89" s="3"/>
-      <c r="J89" s="3" t="s">
+      <c r="J89" s="3"/>
+      <c r="K89" s="3" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A90" s="3">
         <v>4628631077</v>
       </c>
@@ -5064,19 +5395,22 @@
       <c r="E90" s="3">
         <v>7903925678</v>
       </c>
-      <c r="F90" s="3">
+      <c r="F90" s="3" t="s">
+        <v>710</v>
+      </c>
+      <c r="G90" s="3">
         <v>870</v>
       </c>
-      <c r="G90" s="3">
+      <c r="H90" s="3">
         <v>3236</v>
       </c>
-      <c r="H90" s="3"/>
       <c r="I90" s="3"/>
-      <c r="J90" s="3" t="s">
+      <c r="J90" s="3"/>
+      <c r="K90" s="3" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A91" s="3">
         <v>3403434409</v>
       </c>
@@ -5092,19 +5426,22 @@
       <c r="E91" s="3">
         <v>7004148464</v>
       </c>
-      <c r="F91" s="3">
+      <c r="F91" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="G91" s="3">
         <v>823</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>3203</v>
       </c>
-      <c r="H91" s="3"/>
       <c r="I91" s="3"/>
-      <c r="J91" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J91" s="3"/>
+      <c r="K91" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A92" s="3">
         <v>7082474913</v>
       </c>
@@ -5120,21 +5457,24 @@
       <c r="E92" s="3">
         <v>8825101052</v>
       </c>
-      <c r="F92" s="3">
+      <c r="F92" s="3" t="s">
+        <v>711</v>
+      </c>
+      <c r="G92" s="3">
         <v>885</v>
       </c>
-      <c r="G92" s="3">
+      <c r="H92" s="3">
         <v>118</v>
       </c>
-      <c r="H92" s="3" t="s">
+      <c r="I92" s="3" t="s">
         <v>494</v>
       </c>
-      <c r="I92" s="3"/>
-      <c r="J92" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J92" s="3"/>
+      <c r="K92" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A93" s="3">
         <v>1293314852</v>
       </c>
@@ -5150,19 +5490,22 @@
       <c r="E93" s="3">
         <v>9934365755</v>
       </c>
-      <c r="F93" s="3">
+      <c r="F93" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="G93" s="3">
         <v>715</v>
       </c>
-      <c r="G93" s="3">
+      <c r="H93" s="3">
         <v>3205</v>
       </c>
-      <c r="H93" s="3"/>
       <c r="I93" s="3"/>
-      <c r="J93" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J93" s="3"/>
+      <c r="K93" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A94" s="3">
         <v>1419823187</v>
       </c>
@@ -5178,21 +5521,24 @@
       <c r="E94" s="3">
         <v>9931568322</v>
       </c>
-      <c r="F94" s="3">
+      <c r="F94" s="3" t="s">
+        <v>724</v>
+      </c>
+      <c r="G94" s="3">
         <v>834</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>3229</v>
       </c>
-      <c r="H94" s="3" t="s">
+      <c r="I94" s="3" t="s">
         <v>496</v>
       </c>
-      <c r="I94" s="3"/>
-      <c r="J94" s="3" t="s">
+      <c r="J94" s="3"/>
+      <c r="K94" s="3" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A95" s="3">
         <v>4903357331</v>
       </c>
@@ -5206,19 +5552,22 @@
       <c r="E95" s="3">
         <v>7004215297</v>
       </c>
-      <c r="F95" s="3">
+      <c r="F95" s="3" t="s">
+        <v>708</v>
+      </c>
+      <c r="G95" s="3">
         <v>847</v>
       </c>
-      <c r="G95" s="3">
+      <c r="H95" s="3">
         <v>3981</v>
       </c>
-      <c r="H95" s="3"/>
       <c r="I95" s="3"/>
-      <c r="J95" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J95" s="3"/>
+      <c r="K95" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A96" s="3">
         <v>8248798216</v>
       </c>
@@ -5234,23 +5583,26 @@
       <c r="E96" s="3">
         <v>8340226346</v>
       </c>
-      <c r="F96" s="3">
+      <c r="F96" s="3" t="s">
+        <v>711</v>
+      </c>
+      <c r="G96" s="3">
         <v>890</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>3279</v>
       </c>
-      <c r="H96" s="3" t="s">
+      <c r="I96" s="3" t="s">
         <v>498</v>
       </c>
-      <c r="I96" s="3" t="s">
+      <c r="J96" s="3" t="s">
         <v>499</v>
       </c>
-      <c r="J96" s="3" t="s">
+      <c r="K96" s="3" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A97" s="3">
         <v>7618390488</v>
       </c>
@@ -5266,19 +5618,22 @@
       <c r="E97" s="3">
         <v>9431630402</v>
       </c>
-      <c r="F97" s="3">
+      <c r="F97" s="3" t="s">
+        <v>708</v>
+      </c>
+      <c r="G97" s="3">
         <v>880</v>
       </c>
-      <c r="G97" s="3">
+      <c r="H97" s="3">
         <v>3842</v>
       </c>
-      <c r="H97" s="3"/>
       <c r="I97" s="3"/>
-      <c r="J97" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J97" s="3"/>
+      <c r="K97" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A98" s="3">
         <v>5696997655</v>
       </c>
@@ -5294,19 +5649,22 @@
       <c r="E98" s="3">
         <v>7909009544</v>
       </c>
-      <c r="F98" s="3">
+      <c r="F98" s="3" t="s">
+        <v>721</v>
+      </c>
+      <c r="G98" s="3">
         <v>825</v>
       </c>
-      <c r="G98" s="3">
+      <c r="H98" s="3">
         <v>3227</v>
       </c>
-      <c r="H98" s="3"/>
       <c r="I98" s="3"/>
-      <c r="J98" s="3" t="s">
+      <c r="J98" s="3"/>
+      <c r="K98" s="3" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A99" s="3">
         <v>6035251572</v>
       </c>
@@ -5322,19 +5680,22 @@
       <c r="E99" s="3">
         <v>7004576952</v>
       </c>
-      <c r="F99" s="3">
+      <c r="F99" s="3" t="s">
+        <v>717</v>
+      </c>
+      <c r="G99" s="3">
         <v>872</v>
       </c>
-      <c r="G99" s="3">
+      <c r="H99" s="3">
         <v>3237</v>
       </c>
-      <c r="H99" s="3"/>
       <c r="I99" s="3"/>
-      <c r="J99" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J99" s="3"/>
+      <c r="K99" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A100" s="3">
         <v>7780599466</v>
       </c>
@@ -5350,19 +5711,22 @@
       <c r="E100" s="3">
         <v>9431150571</v>
       </c>
-      <c r="F100" s="3">
+      <c r="F100" s="3" t="s">
+        <v>723</v>
+      </c>
+      <c r="G100" s="3">
         <v>878</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>3997</v>
       </c>
-      <c r="H100" s="3"/>
       <c r="I100" s="3"/>
-      <c r="J100" s="3" t="s">
+      <c r="J100" s="3"/>
+      <c r="K100" s="3" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A101" s="3">
         <v>4765437191</v>
       </c>
@@ -5378,19 +5742,22 @@
       <c r="E101" s="3">
         <v>8298970222</v>
       </c>
-      <c r="F101" s="3">
+      <c r="F101" s="3" t="s">
+        <v>726</v>
+      </c>
+      <c r="G101" s="3">
         <v>1268</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>202</v>
       </c>
-      <c r="H101" s="3"/>
       <c r="I101" s="3"/>
-      <c r="J101" s="3" t="s">
+      <c r="J101" s="3"/>
+      <c r="K101" s="3" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A102" s="3">
         <v>3395814592</v>
       </c>
@@ -5406,19 +5773,22 @@
       <c r="E102" s="3">
         <v>9334268703</v>
       </c>
-      <c r="F102" s="3">
+      <c r="F102" s="3" t="s">
+        <v>717</v>
+      </c>
+      <c r="G102" s="3">
         <v>846</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>3855</v>
       </c>
-      <c r="H102" s="3"/>
       <c r="I102" s="3"/>
-      <c r="J102" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J102" s="3"/>
+      <c r="K102" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A103" s="3">
         <v>4192276658</v>
       </c>
@@ -5434,19 +5804,22 @@
       <c r="E103" s="3">
         <v>9334996942</v>
       </c>
-      <c r="F103" s="3">
+      <c r="F103" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="G103" s="3">
         <v>1314</v>
       </c>
-      <c r="G103" s="3">
+      <c r="H103" s="3">
         <v>3296</v>
       </c>
-      <c r="H103" s="3"/>
       <c r="I103" s="3"/>
-      <c r="J103" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J103" s="3"/>
+      <c r="K103" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A104" s="3">
         <v>8628931596</v>
       </c>
@@ -5462,21 +5835,24 @@
       <c r="E104" s="3">
         <v>9709020161</v>
       </c>
-      <c r="F104" s="3">
+      <c r="F104" s="3" t="s">
+        <v>711</v>
+      </c>
+      <c r="G104" s="3">
         <v>832</v>
       </c>
-      <c r="G104" s="3">
+      <c r="H104" s="3">
         <v>3235</v>
       </c>
-      <c r="H104" s="3" t="s">
+      <c r="I104" s="3" t="s">
         <v>501</v>
       </c>
-      <c r="I104" s="3"/>
-      <c r="J104" s="3" t="s">
+      <c r="J104" s="3"/>
+      <c r="K104" s="3" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A105" s="3">
         <v>4915796228</v>
       </c>
@@ -5492,19 +5868,22 @@
       <c r="E105" s="3">
         <v>9304401517</v>
       </c>
-      <c r="F105" s="3">
+      <c r="F105" s="3" t="s">
+        <v>713</v>
+      </c>
+      <c r="G105" s="3">
         <v>836</v>
       </c>
-      <c r="G105" s="3">
+      <c r="H105" s="3">
         <v>3899</v>
       </c>
-      <c r="H105" s="3"/>
       <c r="I105" s="3"/>
-      <c r="J105" s="3" t="s">
+      <c r="J105" s="3"/>
+      <c r="K105" s="3" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A106" s="3">
         <v>7613699637</v>
       </c>
@@ -5520,21 +5899,24 @@
       <c r="E106" s="3">
         <v>8210791282</v>
       </c>
-      <c r="F106" s="3">
+      <c r="F106" s="3" t="s">
+        <v>711</v>
+      </c>
+      <c r="G106" s="3">
         <v>890</v>
       </c>
-      <c r="G106" s="3">
+      <c r="H106" s="3">
         <v>3992</v>
       </c>
-      <c r="H106" s="3" t="s">
+      <c r="I106" s="3" t="s">
         <v>503</v>
       </c>
-      <c r="I106" s="3"/>
-      <c r="J106" s="3" t="s">
+      <c r="J106" s="3"/>
+      <c r="K106" s="3" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A107" s="3">
         <v>6830729927</v>
       </c>
@@ -5550,19 +5932,22 @@
       <c r="E107" s="3">
         <v>9835644064</v>
       </c>
-      <c r="F107" s="3">
+      <c r="F107" s="3" t="s">
+        <v>713</v>
+      </c>
+      <c r="G107" s="3">
         <v>882</v>
       </c>
-      <c r="G107" s="3">
+      <c r="H107" s="3">
         <v>3257</v>
       </c>
-      <c r="H107" s="3"/>
       <c r="I107" s="3"/>
-      <c r="J107" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J107" s="3"/>
+      <c r="K107" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A108" s="3">
         <v>7334582506</v>
       </c>
@@ -5578,19 +5963,22 @@
       <c r="E108" s="3">
         <v>8340324335</v>
       </c>
-      <c r="F108" s="3">
+      <c r="F108" s="3" t="s">
+        <v>710</v>
+      </c>
+      <c r="G108" s="3">
         <v>1300</v>
       </c>
-      <c r="G108" s="3">
+      <c r="H108" s="3">
         <v>3254</v>
       </c>
-      <c r="H108" s="3"/>
       <c r="I108" s="3"/>
-      <c r="J108" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J108" s="3"/>
+      <c r="K108" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A109" s="3">
         <v>3060990296</v>
       </c>
@@ -5604,19 +5992,22 @@
       <c r="E109" s="3">
         <v>8757441514</v>
       </c>
-      <c r="F109" s="3">
+      <c r="F109" s="3" t="s">
+        <v>717</v>
+      </c>
+      <c r="G109" s="3">
         <v>837</v>
       </c>
-      <c r="G109" s="3">
+      <c r="H109" s="3">
         <v>3238</v>
       </c>
-      <c r="H109" s="3"/>
       <c r="I109" s="3"/>
-      <c r="J109" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J109" s="3"/>
+      <c r="K109" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="110" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A110" s="3">
         <v>5237691014</v>
       </c>
@@ -5632,19 +6023,22 @@
       <c r="E110" s="3">
         <v>8252340271</v>
       </c>
-      <c r="F110" s="3">
+      <c r="F110" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="G110" s="3">
         <v>1221</v>
       </c>
-      <c r="G110" s="3">
+      <c r="H110" s="3">
         <v>3804</v>
       </c>
-      <c r="H110" s="3"/>
       <c r="I110" s="3"/>
-      <c r="J110" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J110" s="3"/>
+      <c r="K110" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="111" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A111" s="3">
         <v>8278959422</v>
       </c>
@@ -5660,19 +6054,22 @@
       <c r="E111" s="3">
         <v>6204419576</v>
       </c>
-      <c r="F111" s="3">
+      <c r="F111" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="G111" s="3">
         <v>1221</v>
       </c>
-      <c r="G111" s="3">
+      <c r="H111" s="3">
         <v>3858</v>
       </c>
-      <c r="H111" s="3"/>
       <c r="I111" s="3"/>
-      <c r="J111" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J111" s="3"/>
+      <c r="K111" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A112" s="3">
         <v>2689066633</v>
       </c>
@@ -5688,19 +6085,22 @@
       <c r="E112" s="3">
         <v>8789586640</v>
       </c>
-      <c r="F112" s="3">
+      <c r="F112" s="3" t="s">
+        <v>708</v>
+      </c>
+      <c r="G112" s="3">
         <v>888</v>
       </c>
-      <c r="G112" s="3">
+      <c r="H112" s="3">
         <v>3828</v>
       </c>
-      <c r="H112" s="3"/>
       <c r="I112" s="3"/>
-      <c r="J112" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J112" s="3"/>
+      <c r="K112" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="113" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A113" s="3">
         <v>5068939714</v>
       </c>
@@ -5716,19 +6116,22 @@
       <c r="E113" s="3">
         <v>7004690943</v>
       </c>
-      <c r="F113" s="3">
+      <c r="F113" s="3" t="s">
+        <v>708</v>
+      </c>
+      <c r="G113" s="3">
         <v>1297</v>
       </c>
-      <c r="G113" s="3">
+      <c r="H113" s="3">
         <v>3131</v>
       </c>
-      <c r="H113" s="3"/>
       <c r="I113" s="3"/>
-      <c r="J113" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J113" s="3"/>
+      <c r="K113" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="114" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A114" s="3">
         <v>6248928254</v>
       </c>
@@ -5744,21 +6147,24 @@
       <c r="E114" s="3">
         <v>9431524700</v>
       </c>
-      <c r="F114" s="3">
+      <c r="F114" s="3" t="s">
+        <v>711</v>
+      </c>
+      <c r="G114" s="3">
         <v>4011</v>
       </c>
-      <c r="G114" s="3">
+      <c r="H114" s="3">
         <v>3244</v>
       </c>
-      <c r="H114" s="3" t="s">
+      <c r="I114" s="3" t="s">
         <v>499</v>
       </c>
-      <c r="I114" s="3"/>
-      <c r="J114" s="3" t="s">
+      <c r="J114" s="3"/>
+      <c r="K114" s="3" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A115" s="3">
         <v>4199835065</v>
       </c>
@@ -5774,19 +6180,22 @@
       <c r="E115" s="3">
         <v>9835925014</v>
       </c>
-      <c r="F115" s="3">
+      <c r="F115" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="G115" s="3">
         <v>820</v>
       </c>
-      <c r="G115" s="3">
+      <c r="H115" s="3">
         <v>3281</v>
       </c>
-      <c r="H115" s="3"/>
       <c r="I115" s="3"/>
-      <c r="J115" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J115" s="3"/>
+      <c r="K115" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="116" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A116" s="3">
         <v>6270874763</v>
       </c>
@@ -5800,19 +6209,22 @@
       <c r="E116" s="3">
         <v>7004289539</v>
       </c>
-      <c r="F116" s="3">
+      <c r="F116" s="3" t="s">
+        <v>708</v>
+      </c>
+      <c r="G116" s="3">
         <v>878</v>
       </c>
-      <c r="G116" s="3">
+      <c r="H116" s="3">
         <v>3814</v>
       </c>
-      <c r="H116" s="3"/>
       <c r="I116" s="3"/>
-      <c r="J116" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J116" s="3"/>
+      <c r="K116" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="117" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A117" s="3">
         <v>9070462030</v>
       </c>
@@ -5828,19 +6240,22 @@
       <c r="E117" s="3">
         <v>8340535484</v>
       </c>
-      <c r="F117" s="3">
+      <c r="F117" s="3" t="s">
+        <v>713</v>
+      </c>
+      <c r="G117" s="3">
         <v>810</v>
       </c>
-      <c r="G117" s="3">
+      <c r="H117" s="3">
         <v>3949</v>
       </c>
-      <c r="H117" s="3"/>
       <c r="I117" s="3"/>
-      <c r="J117" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J117" s="3"/>
+      <c r="K117" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="118" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A118" s="3">
         <v>3794029393</v>
       </c>
@@ -5856,19 +6271,22 @@
       <c r="E118" s="3">
         <v>9905766420</v>
       </c>
-      <c r="F118" s="3">
+      <c r="F118" s="3" t="s">
+        <v>708</v>
+      </c>
+      <c r="G118" s="3">
         <v>857</v>
       </c>
-      <c r="G118" s="3">
+      <c r="H118" s="3">
         <v>3271</v>
       </c>
-      <c r="H118" s="3"/>
       <c r="I118" s="3"/>
-      <c r="J118" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J118" s="3"/>
+      <c r="K118" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="119" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A119" s="3">
         <v>7671177388</v>
       </c>
@@ -5884,19 +6302,22 @@
       <c r="E119" s="3">
         <v>6203505770</v>
       </c>
-      <c r="F119" s="3">
+      <c r="F119" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="G119" s="3">
         <v>850</v>
       </c>
-      <c r="G119" s="3">
+      <c r="H119" s="3">
         <v>3999</v>
       </c>
-      <c r="H119" s="3"/>
       <c r="I119" s="3"/>
-      <c r="J119" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J119" s="3"/>
+      <c r="K119" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="120" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A120" s="3">
         <v>6151432328</v>
       </c>
@@ -5912,19 +6333,22 @@
       <c r="E120" s="3">
         <v>9304331481</v>
       </c>
-      <c r="F120" s="3">
+      <c r="F120" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="G120" s="3">
         <v>814</v>
       </c>
-      <c r="G120" s="3">
+      <c r="H120" s="3">
         <v>3255</v>
       </c>
-      <c r="H120" s="3"/>
       <c r="I120" s="3"/>
-      <c r="J120" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J120" s="3"/>
+      <c r="K120" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="121" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A121" s="3">
         <v>6672884434</v>
       </c>
@@ -5940,19 +6364,22 @@
       <c r="E121" s="3">
         <v>7903885125</v>
       </c>
-      <c r="F121" s="3">
+      <c r="F121" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="G121" s="3">
         <v>831</v>
       </c>
-      <c r="G121" s="3">
+      <c r="H121" s="3">
         <v>3905</v>
       </c>
-      <c r="H121" s="3"/>
       <c r="I121" s="3"/>
-      <c r="J121" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="122" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J121" s="3"/>
+      <c r="K121" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="122" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A122" s="3">
         <v>7850048417</v>
       </c>
@@ -5966,19 +6393,22 @@
       <c r="E122" s="3">
         <v>9122333866</v>
       </c>
-      <c r="F122" s="3">
+      <c r="F122" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="G122" s="3">
         <v>825</v>
       </c>
-      <c r="G122" s="3">
+      <c r="H122" s="3">
         <v>3084</v>
       </c>
-      <c r="H122" s="3"/>
       <c r="I122" s="3"/>
-      <c r="J122" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="123" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J122" s="3"/>
+      <c r="K122" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="123" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A123" s="3">
         <v>9065913703</v>
       </c>
@@ -5994,19 +6424,22 @@
       <c r="E123" s="3">
         <v>8709102013</v>
       </c>
-      <c r="F123" s="3">
+      <c r="F123" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="G123" s="3">
         <v>839</v>
       </c>
-      <c r="G123" s="3">
+      <c r="H123" s="3">
         <v>3140</v>
       </c>
-      <c r="H123" s="3"/>
       <c r="I123" s="3"/>
-      <c r="J123" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J123" s="3"/>
+      <c r="K123" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="124" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A124" s="3">
         <v>8376177793</v>
       </c>
@@ -6020,19 +6453,22 @@
       <c r="E124" s="3">
         <v>7903778790</v>
       </c>
-      <c r="F124" s="3">
+      <c r="F124" s="3" t="s">
+        <v>713</v>
+      </c>
+      <c r="G124" s="3">
         <v>810</v>
       </c>
-      <c r="G124" s="3">
+      <c r="H124" s="3">
         <v>3844</v>
       </c>
-      <c r="H124" s="3"/>
       <c r="I124" s="3"/>
-      <c r="J124" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J124" s="3"/>
+      <c r="K124" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="125" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A125" s="3">
         <v>7550982877</v>
       </c>
@@ -6048,19 +6484,22 @@
       <c r="E125" s="3">
         <v>8409804564</v>
       </c>
-      <c r="F125" s="3">
+      <c r="F125" s="3" t="s">
+        <v>708</v>
+      </c>
+      <c r="G125" s="3">
         <v>1318</v>
       </c>
-      <c r="G125" s="3">
+      <c r="H125" s="3">
         <v>3837</v>
       </c>
-      <c r="H125" s="3"/>
       <c r="I125" s="3"/>
-      <c r="J125" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J125" s="3"/>
+      <c r="K125" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="126" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A126" s="3">
         <v>6916519018</v>
       </c>
@@ -6076,19 +6515,22 @@
       <c r="E126" s="3">
         <v>9546213118</v>
       </c>
-      <c r="F126" s="3">
+      <c r="F126" s="3" t="s">
+        <v>717</v>
+      </c>
+      <c r="G126" s="3">
         <v>874</v>
       </c>
-      <c r="G126" s="3">
+      <c r="H126" s="3">
         <v>3272</v>
       </c>
-      <c r="H126" s="3"/>
       <c r="I126" s="3"/>
-      <c r="J126" s="3" t="s">
+      <c r="J126" s="3"/>
+      <c r="K126" s="3" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A127" s="3">
         <v>8196287222</v>
       </c>
@@ -6104,19 +6546,22 @@
       <c r="E127" s="3">
         <v>9934168903</v>
       </c>
-      <c r="F127" s="3">
+      <c r="F127" s="3" t="s">
+        <v>717</v>
+      </c>
+      <c r="G127" s="3">
         <v>874</v>
       </c>
-      <c r="G127" s="3">
+      <c r="H127" s="3">
         <v>3282</v>
       </c>
-      <c r="H127" s="3"/>
       <c r="I127" s="3"/>
-      <c r="J127" s="3" t="s">
+      <c r="J127" s="3"/>
+      <c r="K127" s="3" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A128" s="3">
         <v>7484547570</v>
       </c>
@@ -6132,19 +6577,22 @@
       <c r="E128" s="3">
         <v>8873649555</v>
       </c>
-      <c r="F128" s="3">
+      <c r="F128" s="3" t="s">
+        <v>713</v>
+      </c>
+      <c r="G128" s="3">
         <v>874</v>
       </c>
-      <c r="G128" s="3">
+      <c r="H128" s="3">
         <v>3284</v>
       </c>
-      <c r="H128" s="3"/>
       <c r="I128" s="3"/>
-      <c r="J128" s="3" t="s">
+      <c r="J128" s="3"/>
+      <c r="K128" s="3" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="129" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A129" s="3">
         <v>8281688322</v>
       </c>
@@ -6160,19 +6608,22 @@
       <c r="E129" s="3">
         <v>9835168589</v>
       </c>
-      <c r="F129" s="3">
+      <c r="F129" s="3" t="s">
+        <v>717</v>
+      </c>
+      <c r="G129" s="3">
         <v>837</v>
       </c>
-      <c r="G129" s="3">
+      <c r="H129" s="3">
         <v>3265</v>
       </c>
-      <c r="H129" s="3"/>
       <c r="I129" s="3"/>
-      <c r="J129" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="130" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J129" s="3"/>
+      <c r="K129" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="130" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A130" s="3">
         <v>2092712035</v>
       </c>
@@ -6188,19 +6639,22 @@
       <c r="E130" s="3">
         <v>9334092125</v>
       </c>
-      <c r="F130" s="3">
+      <c r="F130" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="G130" s="3">
         <v>825</v>
       </c>
-      <c r="G130" s="3">
+      <c r="H130" s="3">
         <v>3917</v>
       </c>
-      <c r="H130" s="3"/>
       <c r="I130" s="3"/>
-      <c r="J130" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="131" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J130" s="3"/>
+      <c r="K130" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="131" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A131" s="3">
         <v>4072113231</v>
       </c>
@@ -6214,19 +6668,22 @@
       <c r="E131" s="3">
         <v>9934323967</v>
       </c>
-      <c r="F131" s="3">
+      <c r="F131" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="G131" s="3">
         <v>847</v>
       </c>
-      <c r="G131" s="3">
+      <c r="H131" s="3">
         <v>3981</v>
       </c>
-      <c r="H131" s="3"/>
       <c r="I131" s="3"/>
-      <c r="J131" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="132" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J131" s="3"/>
+      <c r="K131" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="132" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A132" s="3">
         <v>3307724810</v>
       </c>
@@ -6242,21 +6699,24 @@
       <c r="E132" s="3">
         <v>7070192119</v>
       </c>
-      <c r="F132" s="3">
+      <c r="F132" s="3" t="s">
+        <v>714</v>
+      </c>
+      <c r="G132" s="3">
         <v>886</v>
       </c>
-      <c r="G132" s="3">
+      <c r="H132" s="3">
         <v>3985</v>
       </c>
-      <c r="H132" s="3" t="s">
+      <c r="I132" s="3" t="s">
         <v>505</v>
       </c>
-      <c r="I132" s="3"/>
-      <c r="J132" s="3" t="s">
+      <c r="J132" s="3"/>
+      <c r="K132" s="3" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="133" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A133" s="3">
         <v>1999554625</v>
       </c>
@@ -6272,19 +6732,22 @@
       <c r="E133" s="3">
         <v>9934666190</v>
       </c>
-      <c r="F133" s="3">
+      <c r="F133" s="3" t="s">
+        <v>708</v>
+      </c>
+      <c r="G133" s="3">
         <v>828</v>
       </c>
-      <c r="G133" s="3">
+      <c r="H133" s="3">
         <v>3817</v>
       </c>
-      <c r="H133" s="3"/>
       <c r="I133" s="3"/>
-      <c r="J133" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="134" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J133" s="3"/>
+      <c r="K133" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="134" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A134" s="3">
         <v>6552296833</v>
       </c>
@@ -6300,21 +6763,24 @@
       <c r="E134" s="3">
         <v>7061206453</v>
       </c>
-      <c r="F134" s="3">
+      <c r="F134" s="3" t="s">
+        <v>711</v>
+      </c>
+      <c r="G134" s="3">
         <v>4011</v>
       </c>
-      <c r="G134" s="3">
+      <c r="H134" s="3">
         <v>3941</v>
       </c>
-      <c r="H134" s="3" t="s">
+      <c r="I134" s="3" t="s">
         <v>499</v>
       </c>
-      <c r="I134" s="3"/>
-      <c r="J134" s="3" t="s">
+      <c r="J134" s="3"/>
+      <c r="K134" s="3" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="135" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A135" s="3">
         <v>7028026567</v>
       </c>
@@ -6330,21 +6796,24 @@
       <c r="E135" s="3">
         <v>7903646019</v>
       </c>
-      <c r="F135" s="3">
+      <c r="F135" s="3" t="s">
+        <v>711</v>
+      </c>
+      <c r="G135" s="3">
         <v>811</v>
       </c>
-      <c r="G135" s="3">
+      <c r="H135" s="3">
         <v>3848</v>
       </c>
-      <c r="H135" s="3" t="s">
+      <c r="I135" s="3" t="s">
         <v>508</v>
       </c>
-      <c r="I135" s="3"/>
-      <c r="J135" s="3" t="s">
+      <c r="J135" s="3"/>
+      <c r="K135" s="3" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="136" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A136" s="3">
         <v>5217583492</v>
       </c>
@@ -6360,19 +6829,22 @@
       <c r="E136" s="3">
         <v>9835190615</v>
       </c>
-      <c r="F136" s="3">
+      <c r="F136" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="G136" s="3">
         <v>826</v>
       </c>
-      <c r="G136" s="3">
+      <c r="H136" s="3">
         <v>3220</v>
       </c>
-      <c r="H136" s="3"/>
       <c r="I136" s="3"/>
-      <c r="J136" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="137" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J136" s="3"/>
+      <c r="K136" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="137" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A137" s="3">
         <v>6378518993</v>
       </c>
@@ -6388,19 +6860,22 @@
       <c r="E137" s="3">
         <v>9507847509</v>
       </c>
-      <c r="F137" s="3">
+      <c r="F137" s="3" t="s">
+        <v>717</v>
+      </c>
+      <c r="G137" s="3">
         <v>835</v>
       </c>
-      <c r="G137" s="3">
+      <c r="H137" s="3">
         <v>3258</v>
       </c>
-      <c r="H137" s="3"/>
       <c r="I137" s="3"/>
-      <c r="J137" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="138" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J137" s="3"/>
+      <c r="K137" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="138" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A138" s="3">
         <v>5091315887</v>
       </c>
@@ -6416,19 +6891,22 @@
       <c r="E138" s="3">
         <v>7781817742</v>
       </c>
-      <c r="F138" s="3">
+      <c r="F138" s="3" t="s">
+        <v>717</v>
+      </c>
+      <c r="G138" s="3">
         <v>874</v>
       </c>
-      <c r="G138" s="3">
+      <c r="H138" s="3">
         <v>3268</v>
       </c>
-      <c r="H138" s="3"/>
       <c r="I138" s="3"/>
-      <c r="J138" s="3" t="s">
+      <c r="J138" s="3"/>
+      <c r="K138" s="3" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="139" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A139" s="3">
         <v>5488217764</v>
       </c>
@@ -6444,19 +6922,22 @@
       <c r="E139" s="3">
         <v>9973806399</v>
       </c>
-      <c r="F139" s="3">
+      <c r="F139" s="3" t="s">
+        <v>717</v>
+      </c>
+      <c r="G139" s="3">
         <v>857</v>
       </c>
-      <c r="G139" s="3">
+      <c r="H139" s="3">
         <v>3270</v>
       </c>
-      <c r="H139" s="3"/>
       <c r="I139" s="3"/>
-      <c r="J139" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="140" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J139" s="3"/>
+      <c r="K139" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="140" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A140" s="3">
         <v>6044068054</v>
       </c>
@@ -6472,19 +6953,22 @@
       <c r="E140" s="3">
         <v>7488086910</v>
       </c>
-      <c r="F140" s="3">
+      <c r="F140" s="3" t="s">
+        <v>721</v>
+      </c>
+      <c r="G140" s="3">
         <v>879</v>
       </c>
-      <c r="G140" s="3">
+      <c r="H140" s="3">
         <v>3245</v>
       </c>
-      <c r="H140" s="3"/>
       <c r="I140" s="3"/>
-      <c r="J140" s="3" t="s">
+      <c r="J140" s="3"/>
+      <c r="K140" s="3" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="141" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A141" s="3">
         <v>2795135088</v>
       </c>
@@ -6500,19 +6984,22 @@
       <c r="E141" s="3">
         <v>8340761830</v>
       </c>
-      <c r="F141" s="3">
+      <c r="F141" s="3" t="s">
+        <v>712</v>
+      </c>
+      <c r="G141" s="3">
         <v>1357</v>
       </c>
-      <c r="G141" s="3">
+      <c r="H141" s="3">
         <v>3290</v>
       </c>
-      <c r="H141" s="3"/>
       <c r="I141" s="3"/>
-      <c r="J141" s="3" t="s">
+      <c r="J141" s="3"/>
+      <c r="K141" s="3" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="142" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A142" s="3">
         <v>8934578379</v>
       </c>
@@ -6526,19 +7013,22 @@
       <c r="E142" s="3">
         <v>7283000340</v>
       </c>
-      <c r="F142" s="3">
+      <c r="F142" s="3" t="s">
+        <v>715</v>
+      </c>
+      <c r="G142" s="3">
         <v>892</v>
       </c>
-      <c r="G142" s="3">
+      <c r="H142" s="3">
         <v>3927</v>
       </c>
-      <c r="H142" s="3"/>
       <c r="I142" s="3"/>
-      <c r="J142" s="3" t="s">
+      <c r="J142" s="3"/>
+      <c r="K142" s="3" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="143" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A143" s="3">
         <v>6714867933</v>
       </c>
@@ -6554,19 +7044,22 @@
       <c r="E143" s="3">
         <v>9334198130</v>
       </c>
-      <c r="F143" s="3">
+      <c r="F143" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="G143" s="3">
         <v>826</v>
       </c>
-      <c r="G143" s="3">
+      <c r="H143" s="3">
         <v>3812</v>
       </c>
-      <c r="H143" s="3"/>
       <c r="I143" s="3"/>
-      <c r="J143" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="144" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J143" s="3"/>
+      <c r="K143" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="144" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A144" s="3">
         <v>4651873225</v>
       </c>
@@ -6582,19 +7075,22 @@
       <c r="E144" s="3">
         <v>9576615129</v>
       </c>
-      <c r="F144" s="3">
+      <c r="F144" s="3" t="s">
+        <v>708</v>
+      </c>
+      <c r="G144" s="3">
         <v>857</v>
       </c>
-      <c r="G144" s="3">
+      <c r="H144" s="3">
         <v>3240</v>
       </c>
-      <c r="H144" s="3"/>
       <c r="I144" s="3"/>
-      <c r="J144" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="145" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J144" s="3"/>
+      <c r="K144" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="145" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A145" s="3">
         <v>5751042601</v>
       </c>
@@ -6610,19 +7106,22 @@
       <c r="E145" s="3">
         <v>8877000406</v>
       </c>
-      <c r="F145" s="3">
+      <c r="F145" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="G145" s="3">
         <v>1314</v>
       </c>
-      <c r="G145" s="3">
+      <c r="H145" s="3">
         <v>3256</v>
       </c>
-      <c r="H145" s="3"/>
       <c r="I145" s="3"/>
-      <c r="J145" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="146" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J145" s="3"/>
+      <c r="K145" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="146" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A146" s="3">
         <v>2353190987</v>
       </c>
@@ -6638,19 +7137,22 @@
       <c r="E146" s="3">
         <v>7004691036</v>
       </c>
-      <c r="F146" s="3">
+      <c r="F146" s="3" t="s">
+        <v>708</v>
+      </c>
+      <c r="G146" s="3">
         <v>847</v>
       </c>
-      <c r="G146" s="3">
+      <c r="H146" s="3">
         <v>3975</v>
       </c>
-      <c r="H146" s="3"/>
       <c r="I146" s="3"/>
-      <c r="J146" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="147" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J146" s="3"/>
+      <c r="K146" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="147" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A147" s="3">
         <v>2306321602</v>
       </c>
@@ -6666,19 +7168,22 @@
       <c r="E147" s="3">
         <v>9835168557</v>
       </c>
-      <c r="F147" s="3">
+      <c r="F147" s="3" t="s">
+        <v>717</v>
+      </c>
+      <c r="G147" s="3">
         <v>876</v>
       </c>
-      <c r="G147" s="3">
+      <c r="H147" s="3">
         <v>3266</v>
       </c>
-      <c r="H147" s="3"/>
       <c r="I147" s="3"/>
-      <c r="J147" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="148" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J147" s="3"/>
+      <c r="K147" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="148" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A148" s="3">
         <v>1623241122</v>
       </c>
@@ -6694,19 +7199,22 @@
       <c r="E148" s="3">
         <v>8709688226</v>
       </c>
-      <c r="F148" s="3">
+      <c r="F148" s="3" t="s">
+        <v>708</v>
+      </c>
+      <c r="G148" s="3">
         <v>878</v>
       </c>
-      <c r="G148" s="3">
+      <c r="H148" s="3">
         <v>3817</v>
       </c>
-      <c r="H148" s="3"/>
       <c r="I148" s="3"/>
-      <c r="J148" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="149" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J148" s="3"/>
+      <c r="K148" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="149" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A149" s="3">
         <v>5671931467</v>
       </c>
@@ -6720,19 +7228,22 @@
       <c r="E149" s="3">
         <v>9470520001</v>
       </c>
-      <c r="F149" s="3">
+      <c r="F149" s="3" t="s">
+        <v>713</v>
+      </c>
+      <c r="G149" s="3">
         <v>1303</v>
       </c>
-      <c r="G149" s="3">
+      <c r="H149" s="3">
         <v>3967</v>
       </c>
-      <c r="H149" s="3"/>
       <c r="I149" s="3"/>
-      <c r="J149" s="3" t="s">
+      <c r="J149" s="3"/>
+      <c r="K149" s="3" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="150" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A150" s="3">
         <v>6364347255</v>
       </c>
@@ -6746,19 +7257,22 @@
       <c r="E150" s="3">
         <v>9304335854</v>
       </c>
-      <c r="F150" s="3">
+      <c r="F150" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="G150" s="3">
         <v>826</v>
       </c>
-      <c r="G150" s="3">
+      <c r="H150" s="3">
         <v>3285</v>
       </c>
-      <c r="H150" s="3"/>
       <c r="I150" s="3"/>
-      <c r="J150" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="151" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J150" s="3"/>
+      <c r="K150" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="151" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A151" s="3">
         <v>3526429255</v>
       </c>
@@ -6774,19 +7288,22 @@
       <c r="E151" s="3">
         <v>9939725099</v>
       </c>
-      <c r="F151" s="3">
+      <c r="F151" s="3" t="s">
+        <v>716</v>
+      </c>
+      <c r="G151" s="3">
         <v>815</v>
       </c>
-      <c r="G151" s="3">
+      <c r="H151" s="3">
         <v>3983</v>
       </c>
-      <c r="H151" s="3"/>
       <c r="I151" s="3"/>
-      <c r="J151" s="3" t="s">
+      <c r="J151" s="3"/>
+      <c r="K151" s="3" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="152" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A152" s="3">
         <v>5013751151</v>
       </c>
@@ -6800,19 +7317,22 @@
       <c r="E152" s="3">
         <v>7503582453</v>
       </c>
-      <c r="F152" s="3">
+      <c r="F152" s="3" t="s">
+        <v>708</v>
+      </c>
+      <c r="G152" s="3">
         <v>847</v>
       </c>
-      <c r="G152" s="3">
+      <c r="H152" s="3">
         <v>3292</v>
       </c>
-      <c r="H152" s="3"/>
       <c r="I152" s="3"/>
-      <c r="J152" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="153" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J152" s="3"/>
+      <c r="K152" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="153" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A153" s="3">
         <v>6521196327</v>
       </c>
@@ -6828,21 +7348,24 @@
       <c r="E153" s="3">
         <v>7903024617</v>
       </c>
-      <c r="F153" s="3">
+      <c r="F153" s="3" t="s">
+        <v>711</v>
+      </c>
+      <c r="G153" s="3">
         <v>890</v>
       </c>
-      <c r="G153" s="3">
+      <c r="H153" s="3">
         <v>3911</v>
       </c>
-      <c r="H153" s="3" t="s">
+      <c r="I153" s="3" t="s">
         <v>510</v>
       </c>
-      <c r="I153" s="3"/>
-      <c r="J153" s="3" t="s">
+      <c r="J153" s="3"/>
+      <c r="K153" s="3" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="154" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A154" s="3">
         <v>1863397621</v>
       </c>
@@ -6858,19 +7381,22 @@
       <c r="E154" s="3">
         <v>8298069953</v>
       </c>
-      <c r="F154" s="3">
+      <c r="F154" s="3" t="s">
+        <v>713</v>
+      </c>
+      <c r="G154" s="3">
         <v>1303</v>
       </c>
-      <c r="G154" s="3">
+      <c r="H154" s="3">
         <v>3967</v>
       </c>
-      <c r="H154" s="3"/>
       <c r="I154" s="3"/>
-      <c r="J154" s="3" t="s">
+      <c r="J154" s="3"/>
+      <c r="K154" s="3" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="155" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A155" s="3">
         <v>2519343006</v>
       </c>
@@ -6884,19 +7410,22 @@
       <c r="E155" s="3">
         <v>8700177325</v>
       </c>
-      <c r="F155" s="3">
+      <c r="F155" s="3" t="s">
+        <v>713</v>
+      </c>
+      <c r="G155" s="3">
         <v>1303</v>
       </c>
-      <c r="G155" s="3">
+      <c r="H155" s="3">
         <v>3926</v>
       </c>
-      <c r="H155" s="3"/>
       <c r="I155" s="3"/>
-      <c r="J155" s="3" t="s">
+      <c r="J155" s="3"/>
+      <c r="K155" s="3" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="156" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A156" s="3">
         <v>8559314869</v>
       </c>
@@ -6910,19 +7439,22 @@
       <c r="E156" s="3">
         <v>9304533352</v>
       </c>
-      <c r="F156" s="3">
+      <c r="F156" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="G156" s="3">
         <v>826</v>
       </c>
-      <c r="G156" s="3">
+      <c r="H156" s="3">
         <v>3986</v>
       </c>
-      <c r="H156" s="3"/>
       <c r="I156" s="3"/>
-      <c r="J156" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="157" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J156" s="3"/>
+      <c r="K156" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="157" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A157" s="3">
         <v>2300491438</v>
       </c>
@@ -6938,19 +7470,22 @@
       <c r="E157" s="3">
         <v>8292335650</v>
       </c>
-      <c r="F157" s="3">
+      <c r="F157" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="G157" s="3">
         <v>824</v>
       </c>
-      <c r="G157" s="3">
+      <c r="H157" s="3">
         <v>3885</v>
       </c>
-      <c r="H157" s="3"/>
       <c r="I157" s="3"/>
-      <c r="J157" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="158" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J157" s="3"/>
+      <c r="K157" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="158" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A158" s="3">
         <v>8805235250</v>
       </c>
@@ -6966,19 +7501,22 @@
       <c r="E158" s="3">
         <v>9905770045</v>
       </c>
-      <c r="F158" s="3">
+      <c r="F158" s="3" t="s">
+        <v>713</v>
+      </c>
+      <c r="G158" s="3">
         <v>1303</v>
       </c>
-      <c r="G158" s="3">
+      <c r="H158" s="3">
         <v>3859</v>
       </c>
-      <c r="H158" s="3"/>
       <c r="I158" s="3"/>
-      <c r="J158" s="3" t="s">
+      <c r="J158" s="3"/>
+      <c r="K158" s="3" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="159" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A159" s="3">
         <v>4897744570</v>
       </c>
@@ -6994,21 +7532,24 @@
       <c r="E159" s="3">
         <v>9031781786</v>
       </c>
-      <c r="F159" s="3">
+      <c r="F159" s="3" t="s">
+        <v>711</v>
+      </c>
+      <c r="G159" s="3">
         <v>844</v>
       </c>
-      <c r="G159" s="3">
+      <c r="H159" s="3">
         <v>3964</v>
       </c>
-      <c r="H159" s="3" t="s">
+      <c r="I159" s="3" t="s">
         <v>512</v>
       </c>
-      <c r="I159" s="3"/>
-      <c r="J159" s="3" t="s">
+      <c r="J159" s="3"/>
+      <c r="K159" s="3" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="160" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A160" s="3">
         <v>6598056548</v>
       </c>
@@ -7024,19 +7565,22 @@
       <c r="E160" s="3">
         <v>9546918167</v>
       </c>
-      <c r="F160" s="3">
+      <c r="F160" s="3" t="s">
+        <v>712</v>
+      </c>
+      <c r="G160" s="3">
         <v>1249</v>
       </c>
-      <c r="G160" s="3">
+      <c r="H160" s="3">
         <v>3291</v>
       </c>
-      <c r="H160" s="3"/>
       <c r="I160" s="3"/>
-      <c r="J160" s="3" t="s">
+      <c r="J160" s="3"/>
+      <c r="K160" s="3" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="161" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A161" s="3">
         <v>3880439395</v>
       </c>
@@ -7052,19 +7596,22 @@
       <c r="E161" s="3">
         <v>9955940448</v>
       </c>
-      <c r="F161" s="3">
+      <c r="F161" s="3" t="s">
+        <v>712</v>
+      </c>
+      <c r="G161" s="3">
         <v>1357</v>
       </c>
-      <c r="G161" s="3">
+      <c r="H161" s="3">
         <v>3290</v>
       </c>
-      <c r="H161" s="3"/>
       <c r="I161" s="3"/>
-      <c r="J161" s="3" t="s">
+      <c r="J161" s="3"/>
+      <c r="K161" s="3" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="162" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A162" s="3">
         <v>3062655981</v>
       </c>
@@ -7080,23 +7627,26 @@
       <c r="E162" s="3">
         <v>9334651478</v>
       </c>
-      <c r="F162" s="3">
+      <c r="F162" s="3" t="s">
+        <v>711</v>
+      </c>
+      <c r="G162" s="3">
         <v>4011</v>
       </c>
-      <c r="G162" s="3">
+      <c r="H162" s="3">
         <v>3871</v>
       </c>
-      <c r="H162" s="3" t="s">
+      <c r="I162" s="3" t="s">
         <v>514</v>
       </c>
-      <c r="I162" s="3" t="s">
+      <c r="J162" s="3" t="s">
         <v>499</v>
       </c>
-      <c r="J162" s="3" t="s">
+      <c r="K162" s="3" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="163" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A163" s="3">
         <v>1367325676</v>
       </c>
@@ -7112,19 +7662,22 @@
       <c r="E163" s="3">
         <v>8986880070</v>
       </c>
-      <c r="F163" s="3">
+      <c r="F163" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="G163" s="3">
         <v>870</v>
       </c>
-      <c r="G163" s="3">
+      <c r="H163" s="3">
         <v>3274</v>
       </c>
-      <c r="H163" s="3"/>
       <c r="I163" s="3"/>
-      <c r="J163" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="164" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J163" s="3"/>
+      <c r="K163" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="164" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A164" s="3">
         <v>2579484786</v>
       </c>
@@ -7140,21 +7693,24 @@
       <c r="E164" s="3">
         <v>7004312964</v>
       </c>
-      <c r="F164" s="3">
+      <c r="F164" s="3" t="s">
+        <v>711</v>
+      </c>
+      <c r="G164" s="3">
         <v>890</v>
       </c>
-      <c r="G164" s="3">
+      <c r="H164" s="3">
         <v>3809</v>
       </c>
-      <c r="H164" s="3" t="s">
+      <c r="I164" s="3" t="s">
         <v>510</v>
       </c>
-      <c r="I164" s="3"/>
-      <c r="J164" s="3" t="s">
+      <c r="J164" s="3"/>
+      <c r="K164" s="3" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="165" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A165" s="3">
         <v>4772946395</v>
       </c>
@@ -7168,19 +7724,22 @@
       <c r="E165" s="3">
         <v>9635212075</v>
       </c>
-      <c r="F165" s="3">
+      <c r="F165" s="3" t="s">
+        <v>719</v>
+      </c>
+      <c r="G165" s="3">
         <v>656</v>
       </c>
-      <c r="G165" s="3">
+      <c r="H165" s="3">
         <v>201</v>
       </c>
-      <c r="H165" s="3"/>
       <c r="I165" s="3"/>
-      <c r="J165" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="166" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J165" s="3"/>
+      <c r="K165" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="166" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A166" s="3">
         <v>6860022656</v>
       </c>
@@ -7194,19 +7753,22 @@
       <c r="E166" s="3">
         <v>9334915194</v>
       </c>
-      <c r="F166" s="3">
+      <c r="F166" s="3" t="s">
+        <v>708</v>
+      </c>
+      <c r="G166" s="3">
         <v>828</v>
       </c>
-      <c r="G166" s="3">
+      <c r="H166" s="3">
         <v>3817</v>
       </c>
-      <c r="H166" s="3"/>
       <c r="I166" s="3"/>
-      <c r="J166" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="167" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J166" s="3"/>
+      <c r="K166" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="167" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A167" s="3">
         <v>1772556727</v>
       </c>
@@ -7222,19 +7784,22 @@
       <c r="E167" s="3">
         <v>8409540952</v>
       </c>
-      <c r="F167" s="3">
+      <c r="F167" s="3" t="s">
+        <v>713</v>
+      </c>
+      <c r="G167" s="3">
         <v>882</v>
       </c>
-      <c r="G167" s="3">
+      <c r="H167" s="3">
         <v>3830</v>
       </c>
-      <c r="H167" s="3"/>
       <c r="I167" s="3"/>
-      <c r="J167" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="168" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J167" s="3"/>
+      <c r="K167" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="168" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A168" s="3">
         <v>4383088045</v>
       </c>
@@ -7250,19 +7815,22 @@
       <c r="E168" s="3">
         <v>9931563181</v>
       </c>
-      <c r="F168" s="3">
+      <c r="F168" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="G168" s="3">
         <v>819</v>
       </c>
-      <c r="G168" s="3">
+      <c r="H168" s="3">
         <v>3805</v>
       </c>
-      <c r="H168" s="3"/>
       <c r="I168" s="3"/>
-      <c r="J168" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="169" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J168" s="3"/>
+      <c r="K168" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="169" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A169" s="3">
         <v>6412942009</v>
       </c>
@@ -7276,19 +7844,22 @@
       <c r="E169" s="3">
         <v>9534132097</v>
       </c>
-      <c r="F169" s="3">
+      <c r="F169" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="G169" s="3">
         <v>819</v>
       </c>
-      <c r="G169" s="3">
+      <c r="H169" s="3">
         <v>3937</v>
       </c>
-      <c r="H169" s="3"/>
       <c r="I169" s="3"/>
-      <c r="J169" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="170" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J169" s="3"/>
+      <c r="K169" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="170" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A170" s="3">
         <v>7314937389</v>
       </c>
@@ -7304,19 +7875,22 @@
       <c r="E170" s="3">
         <v>9471185628</v>
       </c>
-      <c r="F170" s="3">
+      <c r="F170" s="3" t="s">
+        <v>715</v>
+      </c>
+      <c r="G170" s="3">
         <v>892</v>
       </c>
-      <c r="G170" s="3">
+      <c r="H170" s="3">
         <v>3961</v>
       </c>
-      <c r="H170" s="3"/>
       <c r="I170" s="3"/>
-      <c r="J170" s="3" t="s">
+      <c r="J170" s="3"/>
+      <c r="K170" s="3" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="171" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A171" s="3">
         <v>7647283369</v>
       </c>
@@ -7332,19 +7906,22 @@
       <c r="E171" s="3">
         <v>9431574156</v>
       </c>
-      <c r="F171" s="3">
+      <c r="F171" s="3" t="s">
+        <v>713</v>
+      </c>
+      <c r="G171" s="3">
         <v>882</v>
       </c>
-      <c r="G171" s="3">
+      <c r="H171" s="3">
         <v>3839</v>
       </c>
-      <c r="H171" s="3"/>
       <c r="I171" s="3"/>
-      <c r="J171" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="172" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J171" s="3"/>
+      <c r="K171" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="172" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A172" s="3">
         <v>5795719537</v>
       </c>
@@ -7358,19 +7935,22 @@
       <c r="E172" s="3">
         <v>9304494537</v>
       </c>
-      <c r="F172" s="3">
+      <c r="F172" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="G172" s="3">
         <v>838</v>
       </c>
-      <c r="G172" s="3">
+      <c r="H172" s="3">
         <v>3831</v>
       </c>
-      <c r="H172" s="3"/>
       <c r="I172" s="3"/>
-      <c r="J172" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="173" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J172" s="3"/>
+      <c r="K172" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="173" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A173" s="3">
         <v>2785954584</v>
       </c>
@@ -7386,19 +7966,22 @@
       <c r="E173" s="3">
         <v>9431741666</v>
       </c>
-      <c r="F173" s="3">
+      <c r="F173" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="G173" s="3">
         <v>837</v>
       </c>
-      <c r="G173" s="3">
+      <c r="H173" s="3">
         <v>3889</v>
       </c>
-      <c r="H173" s="3"/>
       <c r="I173" s="3"/>
-      <c r="J173" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="174" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J173" s="3"/>
+      <c r="K173" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="174" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A174" s="3">
         <v>5952977070</v>
       </c>
@@ -7414,21 +7997,24 @@
       <c r="E174" s="3">
         <v>8340585985</v>
       </c>
-      <c r="F174" s="3">
+      <c r="F174" s="3" t="s">
+        <v>711</v>
+      </c>
+      <c r="G174" s="3">
         <v>890</v>
       </c>
-      <c r="G174" s="3">
+      <c r="H174" s="3">
         <v>3911</v>
       </c>
-      <c r="H174" s="3" t="s">
+      <c r="I174" s="3" t="s">
         <v>510</v>
       </c>
-      <c r="I174" s="3"/>
-      <c r="J174" s="3" t="s">
+      <c r="J174" s="3"/>
+      <c r="K174" s="3" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="175" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A175" s="3">
         <v>7456677289</v>
       </c>
@@ -7444,19 +8030,22 @@
       <c r="E175" s="3">
         <v>9334486403</v>
       </c>
-      <c r="F175" s="3">
+      <c r="F175" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="G175" s="3">
         <v>826</v>
       </c>
-      <c r="G175" s="3">
+      <c r="H175" s="3">
         <v>3826</v>
       </c>
-      <c r="H175" s="3"/>
       <c r="I175" s="3"/>
-      <c r="J175" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="176" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J175" s="3"/>
+      <c r="K175" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="176" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A176" s="3">
         <v>1188082699</v>
       </c>
@@ -7472,19 +8061,22 @@
       <c r="E176" s="3">
         <v>9835506592</v>
       </c>
-      <c r="F176" s="3">
+      <c r="F176" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="G176" s="3">
         <v>875</v>
       </c>
-      <c r="G176" s="3">
+      <c r="H176" s="3">
         <v>3192</v>
       </c>
-      <c r="H176" s="3"/>
       <c r="I176" s="3"/>
-      <c r="J176" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="177" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J176" s="3"/>
+      <c r="K176" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="177" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A177" s="3">
         <v>6656211665</v>
       </c>
@@ -7500,21 +8092,24 @@
       <c r="E177" s="3">
         <v>9431542996</v>
       </c>
-      <c r="F177" s="3">
+      <c r="F177" s="3" t="s">
+        <v>711</v>
+      </c>
+      <c r="G177" s="3">
         <v>844</v>
       </c>
-      <c r="G177" s="3">
+      <c r="H177" s="3">
         <v>3904</v>
       </c>
-      <c r="H177" s="3" t="s">
+      <c r="I177" s="3" t="s">
         <v>518</v>
       </c>
-      <c r="I177" s="3"/>
-      <c r="J177" s="3" t="s">
+      <c r="J177" s="3"/>
+      <c r="K177" s="3" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="178" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A178" s="3">
         <v>1441026587</v>
       </c>
@@ -7530,21 +8125,24 @@
       <c r="E178" s="3">
         <v>9570662555</v>
       </c>
-      <c r="F178" s="3">
+      <c r="F178" s="3" t="s">
+        <v>711</v>
+      </c>
+      <c r="G178" s="3">
         <v>890</v>
       </c>
-      <c r="G178" s="3">
+      <c r="H178" s="3">
         <v>3834</v>
       </c>
-      <c r="H178" s="3" t="s">
+      <c r="I178" s="3" t="s">
         <v>499</v>
       </c>
-      <c r="I178" s="3"/>
-      <c r="J178" s="3" t="s">
+      <c r="J178" s="3"/>
+      <c r="K178" s="3" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="179" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A179" s="3">
         <v>3579877656</v>
       </c>
@@ -7558,19 +8156,22 @@
       <c r="E179" s="3">
         <v>7061438113</v>
       </c>
-      <c r="F179" s="3">
+      <c r="F179" s="3" t="s">
+        <v>708</v>
+      </c>
+      <c r="G179" s="3">
         <v>880</v>
       </c>
-      <c r="G179" s="3">
+      <c r="H179" s="3">
         <v>3842</v>
       </c>
-      <c r="H179" s="3"/>
       <c r="I179" s="3"/>
-      <c r="J179" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="180" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J179" s="3"/>
+      <c r="K179" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="180" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A180" s="3">
         <v>8320458644</v>
       </c>
@@ -7584,19 +8185,22 @@
       <c r="E180" s="3">
         <v>9431164996</v>
       </c>
-      <c r="F180" s="3">
+      <c r="F180" s="3" t="s">
+        <v>723</v>
+      </c>
+      <c r="G180" s="3">
         <v>801</v>
       </c>
-      <c r="G180" s="3">
+      <c r="H180" s="3">
         <v>3968</v>
       </c>
-      <c r="H180" s="3"/>
       <c r="I180" s="3"/>
-      <c r="J180" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="181" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J180" s="3"/>
+      <c r="K180" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="181" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A181" s="3">
         <v>3350895733</v>
       </c>
@@ -7612,19 +8216,22 @@
       <c r="E181" s="3">
         <v>9798256365</v>
       </c>
-      <c r="F181" s="3">
+      <c r="F181" s="3" t="s">
+        <v>713</v>
+      </c>
+      <c r="G181" s="3">
         <v>882</v>
       </c>
-      <c r="G181" s="3">
+      <c r="H181" s="3">
         <v>3840</v>
       </c>
-      <c r="H181" s="3"/>
       <c r="I181" s="3"/>
-      <c r="J181" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="182" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J181" s="3"/>
+      <c r="K181" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="182" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A182" s="3">
         <v>4805111999</v>
       </c>
@@ -7640,23 +8247,26 @@
       <c r="E182" s="3">
         <v>8987745409</v>
       </c>
-      <c r="F182" s="3">
+      <c r="F182" s="3" t="s">
+        <v>724</v>
+      </c>
+      <c r="G182" s="3">
         <v>890</v>
       </c>
-      <c r="G182" s="3">
+      <c r="H182" s="3">
         <v>3866</v>
-      </c>
-      <c r="H182" s="3" t="s">
-        <v>474</v>
       </c>
       <c r="I182" s="3" t="s">
         <v>474</v>
       </c>
       <c r="J182" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="K182" s="3" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="183" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A183" s="3">
         <v>5445180158</v>
       </c>
@@ -7672,19 +8282,22 @@
       <c r="E183" s="3">
         <v>7903244542</v>
       </c>
-      <c r="F183" s="3">
+      <c r="F183" s="3" t="s">
+        <v>710</v>
+      </c>
+      <c r="G183" s="3">
         <v>827</v>
       </c>
-      <c r="G183" s="3">
+      <c r="H183" s="3">
         <v>3920</v>
       </c>
-      <c r="H183" s="3"/>
       <c r="I183" s="3"/>
-      <c r="J183" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="184" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J183" s="3"/>
+      <c r="K183" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="184" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A184" s="3">
         <v>5042838277</v>
       </c>
@@ -7700,19 +8313,22 @@
       <c r="E184" s="3">
         <v>7903719826</v>
       </c>
-      <c r="F184" s="3">
+      <c r="F184" s="3" t="s">
+        <v>713</v>
+      </c>
+      <c r="G184" s="3">
         <v>1303</v>
       </c>
-      <c r="G184" s="3">
+      <c r="H184" s="3">
         <v>3895</v>
       </c>
-      <c r="H184" s="3"/>
       <c r="I184" s="3"/>
-      <c r="J184" s="3" t="s">
+      <c r="J184" s="3"/>
+      <c r="K184" s="3" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="185" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A185" s="3">
         <v>6443213937</v>
       </c>
@@ -7728,21 +8344,24 @@
       <c r="E185" s="3">
         <v>9431117662</v>
       </c>
-      <c r="F185" s="3">
+      <c r="F185" s="3" t="s">
+        <v>711</v>
+      </c>
+      <c r="G185" s="3">
         <v>890</v>
       </c>
-      <c r="G185" s="3">
+      <c r="H185" s="3">
         <v>131</v>
       </c>
-      <c r="H185" s="3" t="s">
+      <c r="I185" s="3" t="s">
         <v>474</v>
       </c>
-      <c r="I185" s="3"/>
-      <c r="J185" s="3" t="s">
+      <c r="J185" s="3"/>
+      <c r="K185" s="3" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="186" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A186" s="3">
         <v>6444614161</v>
       </c>
@@ -7758,19 +8377,22 @@
       <c r="E186" s="3">
         <v>7979072298</v>
       </c>
-      <c r="F186" s="3">
+      <c r="F186" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="G186" s="3">
         <v>815</v>
       </c>
-      <c r="G186" s="3">
+      <c r="H186" s="3">
         <v>3910</v>
       </c>
-      <c r="H186" s="3"/>
       <c r="I186" s="3"/>
-      <c r="J186" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="187" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J186" s="3"/>
+      <c r="K186" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="187" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A187" s="3">
         <v>4668486040</v>
       </c>
@@ -7786,19 +8408,22 @@
       <c r="E187" s="3">
         <v>9304325501</v>
       </c>
-      <c r="F187" s="3">
+      <c r="F187" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="G187" s="3">
         <v>822</v>
       </c>
-      <c r="G187" s="3">
+      <c r="H187" s="3">
         <v>3881</v>
       </c>
-      <c r="H187" s="3"/>
       <c r="I187" s="3"/>
-      <c r="J187" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="188" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J187" s="3"/>
+      <c r="K187" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="188" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A188" s="3">
         <v>1297877629</v>
       </c>
@@ -7814,21 +8439,24 @@
       <c r="E188" s="3">
         <v>9801238353</v>
       </c>
-      <c r="F188" s="3">
+      <c r="F188" s="3" t="s">
+        <v>711</v>
+      </c>
+      <c r="G188" s="3">
         <v>844</v>
       </c>
-      <c r="G188" s="3">
+      <c r="H188" s="3">
         <v>3903</v>
       </c>
-      <c r="H188" s="3" t="s">
+      <c r="I188" s="3" t="s">
         <v>523</v>
       </c>
-      <c r="I188" s="3"/>
-      <c r="J188" s="3" t="s">
+      <c r="J188" s="3"/>
+      <c r="K188" s="3" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="189" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A189" s="3">
         <v>3472525793</v>
       </c>
@@ -7842,19 +8470,22 @@
       <c r="E189" s="3">
         <v>9835760060</v>
       </c>
-      <c r="F189" s="3">
+      <c r="F189" s="3" t="s">
+        <v>716</v>
+      </c>
+      <c r="G189" s="3">
         <v>825</v>
       </c>
-      <c r="G189" s="3">
+      <c r="H189" s="3">
         <v>3869</v>
       </c>
-      <c r="H189" s="3"/>
       <c r="I189" s="3"/>
-      <c r="J189" s="3" t="s">
+      <c r="J189" s="3"/>
+      <c r="K189" s="3" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="190" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A190" s="3">
         <v>6833487134</v>
       </c>
@@ -7870,19 +8501,22 @@
       <c r="E190" s="3">
         <v>9431375952</v>
       </c>
-      <c r="F190" s="3">
+      <c r="F190" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="G190" s="3">
         <v>825</v>
       </c>
-      <c r="G190" s="3">
+      <c r="H190" s="3">
         <v>3932</v>
       </c>
-      <c r="H190" s="3"/>
       <c r="I190" s="3"/>
-      <c r="J190" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="191" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J190" s="3"/>
+      <c r="K190" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="191" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A191" s="3">
         <v>3475055686</v>
       </c>
@@ -7896,19 +8530,22 @@
       <c r="E191" s="3">
         <v>7903362721</v>
       </c>
-      <c r="F191" s="3">
+      <c r="F191" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="G191" s="3">
         <v>815</v>
       </c>
-      <c r="G191" s="3">
+      <c r="H191" s="3">
         <v>3910</v>
       </c>
-      <c r="H191" s="3"/>
       <c r="I191" s="3"/>
-      <c r="J191" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="192" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J191" s="3"/>
+      <c r="K191" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="192" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A192" s="3">
         <v>2897042119</v>
       </c>
@@ -7924,21 +8561,24 @@
       <c r="E192" s="3">
         <v>9431381731</v>
       </c>
-      <c r="F192" s="3">
+      <c r="F192" s="3" t="s">
+        <v>711</v>
+      </c>
+      <c r="G192" s="3">
         <v>4011</v>
       </c>
-      <c r="G192" s="3">
+      <c r="H192" s="3">
         <v>3887</v>
       </c>
-      <c r="H192" s="3" t="s">
+      <c r="I192" s="3" t="s">
         <v>499</v>
       </c>
-      <c r="I192" s="3"/>
-      <c r="J192" s="3" t="s">
+      <c r="J192" s="3"/>
+      <c r="K192" s="3" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="193" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A193" s="3">
         <v>8737451302</v>
       </c>
@@ -7952,19 +8592,22 @@
       <c r="E193" s="3">
         <v>7870611208</v>
       </c>
-      <c r="F193" s="3">
+      <c r="F193" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="G193" s="3">
         <v>1323</v>
       </c>
-      <c r="G193" s="3">
+      <c r="H193" s="3">
         <v>3880</v>
       </c>
-      <c r="H193" s="3"/>
       <c r="I193" s="3"/>
-      <c r="J193" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="194" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J193" s="3"/>
+      <c r="K193" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="194" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A194" s="3">
         <v>1163822769</v>
       </c>
@@ -7980,19 +8623,22 @@
       <c r="E194" s="3">
         <v>9386369286</v>
       </c>
-      <c r="F194" s="3">
+      <c r="F194" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="G194" s="3">
         <v>850</v>
       </c>
-      <c r="G194" s="3">
+      <c r="H194" s="3">
         <v>3999</v>
       </c>
-      <c r="H194" s="3"/>
       <c r="I194" s="3"/>
-      <c r="J194" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="195" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J194" s="3"/>
+      <c r="K194" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="195" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A195" s="3">
         <v>5521997030</v>
       </c>
@@ -8006,19 +8652,22 @@
       <c r="E195" s="3">
         <v>9835320090</v>
       </c>
-      <c r="F195" s="3">
+      <c r="F195" s="3" t="s">
+        <v>713</v>
+      </c>
+      <c r="G195" s="3">
         <v>870</v>
       </c>
-      <c r="G195" s="3">
+      <c r="H195" s="3">
         <v>3943</v>
       </c>
-      <c r="H195" s="3"/>
       <c r="I195" s="3"/>
-      <c r="J195" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="196" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J195" s="3"/>
+      <c r="K195" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="196" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A196" s="3">
         <v>4991250698</v>
       </c>
@@ -8032,19 +8681,22 @@
       <c r="E196" s="3">
         <v>9576116157</v>
       </c>
-      <c r="F196" s="3">
+      <c r="F196" s="3" t="s">
+        <v>717</v>
+      </c>
+      <c r="G196" s="3">
         <v>857</v>
       </c>
-      <c r="G196" s="3">
+      <c r="H196" s="3">
         <v>3270</v>
       </c>
-      <c r="H196" s="3"/>
       <c r="I196" s="3"/>
-      <c r="J196" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="197" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J196" s="3"/>
+      <c r="K196" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="197" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A197" s="3">
         <v>7619094759</v>
       </c>
@@ -8060,21 +8712,24 @@
       <c r="E197" s="3">
         <v>9534463285</v>
       </c>
-      <c r="F197" s="3">
+      <c r="F197" s="3" t="s">
+        <v>711</v>
+      </c>
+      <c r="G197" s="3">
         <v>844</v>
       </c>
-      <c r="G197" s="3">
+      <c r="H197" s="3">
         <v>3902</v>
       </c>
-      <c r="H197" s="3" t="s">
+      <c r="I197" s="3" t="s">
         <v>526</v>
       </c>
-      <c r="I197" s="3"/>
-      <c r="J197" s="3" t="s">
+      <c r="J197" s="3"/>
+      <c r="K197" s="3" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="198" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A198" s="3">
         <v>8082129789</v>
       </c>
@@ -8090,19 +8745,22 @@
       <c r="E198" s="3">
         <v>9431337198</v>
       </c>
-      <c r="F198" s="3">
+      <c r="F198" s="3" t="s">
+        <v>710</v>
+      </c>
+      <c r="G198" s="3">
         <v>827</v>
       </c>
-      <c r="G198" s="3">
+      <c r="H198" s="3">
         <v>3921</v>
       </c>
-      <c r="H198" s="3"/>
       <c r="I198" s="3"/>
-      <c r="J198" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="199" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J198" s="3"/>
+      <c r="K198" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="199" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A199" s="3">
         <v>1936579180</v>
       </c>
@@ -8118,19 +8776,22 @@
       <c r="E199" s="3">
         <v>9835107248</v>
       </c>
-      <c r="F199" s="3">
+      <c r="F199" s="3" t="s">
+        <v>717</v>
+      </c>
+      <c r="G199" s="3">
         <v>835</v>
       </c>
-      <c r="G199" s="3">
+      <c r="H199" s="3">
         <v>3938</v>
       </c>
-      <c r="H199" s="3"/>
       <c r="I199" s="3"/>
-      <c r="J199" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="200" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J199" s="3"/>
+      <c r="K199" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="200" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A200" s="3">
         <v>1962495733</v>
       </c>
@@ -8146,19 +8807,22 @@
       <c r="E200" s="3">
         <v>9110062512</v>
       </c>
-      <c r="F200" s="3">
+      <c r="F200" s="3" t="s">
+        <v>723</v>
+      </c>
+      <c r="G200" s="3">
         <v>801</v>
       </c>
-      <c r="G200" s="3">
+      <c r="H200" s="3">
         <v>3950</v>
       </c>
-      <c r="H200" s="3"/>
       <c r="I200" s="3"/>
-      <c r="J200" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="201" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J200" s="3"/>
+      <c r="K200" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="201" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A201" s="3">
         <v>2702931898</v>
       </c>
@@ -8174,19 +8838,22 @@
       <c r="E201" s="3">
         <v>9771834381</v>
       </c>
-      <c r="F201" s="3">
+      <c r="F201" s="3" t="s">
+        <v>713</v>
+      </c>
+      <c r="G201" s="3">
         <v>882</v>
       </c>
-      <c r="G201" s="3">
+      <c r="H201" s="3">
         <v>3872</v>
       </c>
-      <c r="H201" s="3"/>
       <c r="I201" s="3"/>
-      <c r="J201" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="202" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J201" s="3"/>
+      <c r="K201" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="202" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A202" s="3">
         <v>7772584579</v>
       </c>
@@ -8200,19 +8867,22 @@
       <c r="E202" s="3">
         <v>9905598164</v>
       </c>
-      <c r="F202" s="3">
+      <c r="F202" s="3" t="s">
+        <v>713</v>
+      </c>
+      <c r="G202" s="3">
         <v>866</v>
       </c>
-      <c r="G202" s="3">
+      <c r="H202" s="3">
         <v>3862</v>
       </c>
-      <c r="H202" s="3"/>
       <c r="I202" s="3"/>
-      <c r="J202" s="3" t="s">
+      <c r="J202" s="3"/>
+      <c r="K202" s="3" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="203" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A203" s="3">
         <v>6459548335</v>
       </c>
@@ -8228,21 +8898,24 @@
       <c r="E203" s="3">
         <v>9334800378</v>
       </c>
-      <c r="F203" s="3">
+      <c r="F203" s="3" t="s">
+        <v>711</v>
+      </c>
+      <c r="G203" s="3">
         <v>890</v>
       </c>
-      <c r="G203" s="3">
+      <c r="H203" s="3">
         <v>3892</v>
       </c>
-      <c r="H203" s="3" t="s">
+      <c r="I203" s="3" t="s">
         <v>528</v>
       </c>
-      <c r="I203" s="3"/>
-      <c r="J203" s="3" t="s">
+      <c r="J203" s="3"/>
+      <c r="K203" s="3" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="204" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A204" s="3">
         <v>1570669308</v>
       </c>
@@ -8258,19 +8931,22 @@
       <c r="E204" s="3">
         <v>8252778277</v>
       </c>
-      <c r="F204" s="3">
+      <c r="F204" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="G204" s="3">
         <v>814</v>
       </c>
-      <c r="G204" s="3">
+      <c r="H204" s="3">
         <v>3948</v>
       </c>
-      <c r="H204" s="3"/>
       <c r="I204" s="3"/>
-      <c r="J204" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="205" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J204" s="3"/>
+      <c r="K204" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="205" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A205" s="3">
         <v>1682930418</v>
       </c>
@@ -8284,19 +8960,22 @@
       <c r="E205" s="3">
         <v>9334465527</v>
       </c>
-      <c r="F205" s="3">
+      <c r="F205" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="G205" s="3">
         <v>814</v>
       </c>
-      <c r="G205" s="3">
+      <c r="H205" s="3">
         <v>3857</v>
       </c>
-      <c r="H205" s="3"/>
       <c r="I205" s="3"/>
-      <c r="J205" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="206" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J205" s="3"/>
+      <c r="K205" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="206" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A206" s="3">
         <v>4085991855</v>
       </c>
@@ -8312,19 +8991,22 @@
       <c r="E206" s="3">
         <v>7903409791</v>
       </c>
-      <c r="F206" s="3">
+      <c r="F206" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="G206" s="3">
         <v>863</v>
       </c>
-      <c r="G206" s="3">
+      <c r="H206" s="3">
         <v>3929</v>
       </c>
-      <c r="H206" s="3"/>
       <c r="I206" s="3"/>
-      <c r="J206" s="3" t="s">
+      <c r="J206" s="3"/>
+      <c r="K206" s="3" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="207" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A207" s="3">
         <v>6515115933</v>
       </c>
@@ -8340,21 +9022,24 @@
       <c r="E207" s="3">
         <v>9431347841</v>
       </c>
-      <c r="F207" s="3">
+      <c r="F207" s="3" t="s">
+        <v>711</v>
+      </c>
+      <c r="G207" s="3">
         <v>844</v>
       </c>
-      <c r="G207" s="3">
+      <c r="H207" s="3">
         <v>3965</v>
       </c>
-      <c r="H207" s="3" t="s">
+      <c r="I207" s="3" t="s">
         <v>530</v>
       </c>
-      <c r="I207" s="3"/>
-      <c r="J207" s="3" t="s">
+      <c r="J207" s="3"/>
+      <c r="K207" s="3" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="208" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A208" s="3">
         <v>5521898710</v>
       </c>
@@ -8370,21 +9055,24 @@
       <c r="E208" s="3">
         <v>9110973607</v>
       </c>
-      <c r="F208" s="3">
+      <c r="F208" s="3" t="s">
+        <v>711</v>
+      </c>
+      <c r="G208" s="3">
         <v>4011</v>
       </c>
-      <c r="G208" s="3">
+      <c r="H208" s="3">
         <v>3864</v>
       </c>
-      <c r="H208" s="3" t="s">
+      <c r="I208" s="3" t="s">
         <v>532</v>
       </c>
-      <c r="I208" s="3"/>
-      <c r="J208" s="3" t="s">
+      <c r="J208" s="3"/>
+      <c r="K208" s="3" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="209" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A209" s="3">
         <v>2868583648</v>
       </c>
@@ -8400,19 +9088,22 @@
       <c r="E209" s="3">
         <v>8789295417</v>
       </c>
-      <c r="F209" s="3">
+      <c r="F209" s="3" t="s">
+        <v>713</v>
+      </c>
+      <c r="G209" s="3">
         <v>1303</v>
       </c>
-      <c r="G209" s="3">
+      <c r="H209" s="3">
         <v>3854</v>
       </c>
-      <c r="H209" s="3"/>
       <c r="I209" s="3"/>
-      <c r="J209" s="3" t="s">
+      <c r="J209" s="3"/>
+      <c r="K209" s="3" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="210" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A210" s="3">
         <v>7387228722</v>
       </c>
@@ -8428,19 +9119,22 @@
       <c r="E210" s="3">
         <v>9939578978</v>
       </c>
-      <c r="F210" s="3">
+      <c r="F210" s="3" t="s">
+        <v>708</v>
+      </c>
+      <c r="G210" s="3">
         <v>847</v>
       </c>
-      <c r="G210" s="3">
+      <c r="H210" s="3">
         <v>3879</v>
       </c>
-      <c r="H210" s="3"/>
       <c r="I210" s="3"/>
-      <c r="J210" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="211" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J210" s="3"/>
+      <c r="K210" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="211" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A211" s="3">
         <v>8745578803</v>
       </c>
@@ -8456,19 +9150,22 @@
       <c r="E211" s="3">
         <v>8789418730</v>
       </c>
-      <c r="F211" s="3">
+      <c r="F211" s="3" t="s">
+        <v>708</v>
+      </c>
+      <c r="G211" s="3">
         <v>1318</v>
       </c>
-      <c r="G211" s="3">
+      <c r="H211" s="3">
         <v>3853</v>
       </c>
-      <c r="H211" s="3"/>
       <c r="I211" s="3"/>
-      <c r="J211" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="212" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J211" s="3"/>
+      <c r="K211" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="212" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A212" s="3">
         <v>2167791239</v>
       </c>
@@ -8484,19 +9181,22 @@
       <c r="E212" s="3">
         <v>7004827956</v>
       </c>
-      <c r="F212" s="3">
+      <c r="F212" s="3" t="s">
+        <v>708</v>
+      </c>
+      <c r="G212" s="3">
         <v>878</v>
       </c>
-      <c r="G212" s="3">
+      <c r="H212" s="3">
         <v>3884</v>
       </c>
-      <c r="H212" s="3"/>
       <c r="I212" s="3"/>
-      <c r="J212" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="213" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J212" s="3"/>
+      <c r="K212" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="213" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A213" s="3">
         <v>8422396538</v>
       </c>
@@ -8512,21 +9212,24 @@
       <c r="E213" s="3">
         <v>9431751638</v>
       </c>
-      <c r="F213" s="3">
+      <c r="F213" s="3" t="s">
+        <v>711</v>
+      </c>
+      <c r="G213" s="3">
         <v>4011</v>
       </c>
-      <c r="G213" s="3">
+      <c r="H213" s="3">
         <v>3865</v>
       </c>
-      <c r="H213" s="3" t="s">
+      <c r="I213" s="3" t="s">
         <v>534</v>
       </c>
-      <c r="I213" s="3"/>
-      <c r="J213" s="3" t="s">
+      <c r="J213" s="3"/>
+      <c r="K213" s="3" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="214" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A214" s="3">
         <v>1296956106</v>
       </c>
@@ -8542,19 +9245,22 @@
       <c r="E214" s="3">
         <v>8580245866</v>
       </c>
-      <c r="F214" s="3">
+      <c r="F214" s="3" t="s">
+        <v>713</v>
+      </c>
+      <c r="G214" s="3">
         <v>866</v>
       </c>
-      <c r="G214" s="3">
+      <c r="H214" s="3">
         <v>3179</v>
       </c>
-      <c r="H214" s="3"/>
       <c r="I214" s="3"/>
-      <c r="J214" s="3" t="s">
+      <c r="J214" s="3"/>
+      <c r="K214" s="3" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="215" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A215" s="3">
         <v>8679251621</v>
       </c>
@@ -8570,21 +9276,24 @@
       <c r="E215" s="3">
         <v>9334132334</v>
       </c>
-      <c r="F215" s="3">
+      <c r="F215" s="3" t="s">
+        <v>711</v>
+      </c>
+      <c r="G215" s="3">
         <v>4011</v>
       </c>
-      <c r="G215" s="3">
+      <c r="H215" s="3">
         <v>3901</v>
       </c>
-      <c r="H215" s="3" t="s">
+      <c r="I215" s="3" t="s">
         <v>492</v>
       </c>
-      <c r="I215" s="3"/>
-      <c r="J215" s="3" t="s">
+      <c r="J215" s="3"/>
+      <c r="K215" s="3" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="216" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A216" s="3">
         <v>1701531020</v>
       </c>
@@ -8600,21 +9309,24 @@
       <c r="E216" s="3">
         <v>9431349237</v>
       </c>
-      <c r="F216" s="3">
+      <c r="F216" s="3" t="s">
+        <v>711</v>
+      </c>
+      <c r="G216" s="3">
         <v>890</v>
       </c>
-      <c r="G216" s="3">
+      <c r="H216" s="3">
         <v>3892</v>
       </c>
-      <c r="H216" s="3" t="s">
+      <c r="I216" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="I216" s="3"/>
-      <c r="J216" s="3" t="s">
+      <c r="J216" s="3"/>
+      <c r="K216" s="3" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="217" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A217" s="3">
         <v>8933728890</v>
       </c>
@@ -8630,23 +9342,26 @@
       <c r="E217" s="3">
         <v>9431303185</v>
       </c>
-      <c r="F217" s="3">
+      <c r="F217" s="3" t="s">
+        <v>711</v>
+      </c>
+      <c r="G217" s="3">
         <v>890</v>
       </c>
-      <c r="G217" s="3">
+      <c r="H217" s="3">
         <v>3891</v>
       </c>
-      <c r="H217" s="3" t="s">
+      <c r="I217" s="3" t="s">
         <v>538</v>
       </c>
-      <c r="I217" s="3" t="s">
+      <c r="J217" s="3" t="s">
         <v>539</v>
       </c>
-      <c r="J217" s="3" t="s">
+      <c r="K217" s="3" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="218" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A218" s="3">
         <v>5389091540</v>
       </c>
@@ -8662,19 +9377,22 @@
       <c r="E218" s="3">
         <v>9431376691</v>
       </c>
-      <c r="F218" s="3">
+      <c r="F218" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="G218" s="3">
         <v>1314</v>
       </c>
-      <c r="G218" s="3">
+      <c r="H218" s="3">
         <v>3923</v>
       </c>
-      <c r="H218" s="3"/>
       <c r="I218" s="3"/>
-      <c r="J218" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="219" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J218" s="3"/>
+      <c r="K218" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="219" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A219" s="3">
         <v>4224683160</v>
       </c>
@@ -8690,19 +9408,22 @@
       <c r="E219" s="3">
         <v>9431182831</v>
       </c>
-      <c r="F219" s="3">
+      <c r="F219" s="3" t="s">
+        <v>713</v>
+      </c>
+      <c r="G219" s="3">
         <v>1303</v>
       </c>
-      <c r="G219" s="3">
+      <c r="H219" s="3">
         <v>3927</v>
       </c>
-      <c r="H219" s="3"/>
       <c r="I219" s="3"/>
-      <c r="J219" s="3" t="s">
+      <c r="J219" s="3"/>
+      <c r="K219" s="3" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="220" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A220" s="3">
         <v>4630629704</v>
       </c>
@@ -8716,19 +9437,22 @@
       <c r="E220" s="3">
         <v>6200551037</v>
       </c>
-      <c r="F220" s="3">
+      <c r="F220" s="3" t="s">
+        <v>713</v>
+      </c>
+      <c r="G220" s="3">
         <v>870</v>
       </c>
-      <c r="G220" s="3">
+      <c r="H220" s="3">
         <v>3940</v>
       </c>
-      <c r="H220" s="3"/>
       <c r="I220" s="3"/>
-      <c r="J220" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="221" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J220" s="3"/>
+      <c r="K220" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="221" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A221" s="3">
         <v>4681796426</v>
       </c>
@@ -8744,19 +9468,22 @@
       <c r="E221" s="3">
         <v>9835513079</v>
       </c>
-      <c r="F221" s="3">
+      <c r="F221" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="G221" s="3">
         <v>820</v>
       </c>
-      <c r="G221" s="3">
+      <c r="H221" s="3">
         <v>3935</v>
       </c>
-      <c r="H221" s="3"/>
       <c r="I221" s="3"/>
-      <c r="J221" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="222" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J221" s="3"/>
+      <c r="K221" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="222" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A222" s="3">
         <v>2249627620</v>
       </c>
@@ -8772,19 +9499,22 @@
       <c r="E222" s="3">
         <v>9431154373</v>
       </c>
-      <c r="F222" s="3">
+      <c r="F222" s="3" t="s">
+        <v>719</v>
+      </c>
+      <c r="G222" s="3">
         <v>817</v>
       </c>
-      <c r="G222" s="3">
+      <c r="H222" s="3">
         <v>3937</v>
       </c>
-      <c r="H222" s="3"/>
       <c r="I222" s="3"/>
-      <c r="J222" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="223" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J222" s="3"/>
+      <c r="K222" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="223" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A223" s="3">
         <v>5592176008</v>
       </c>
@@ -8800,19 +9530,22 @@
       <c r="E223" s="3">
         <v>9308525125</v>
       </c>
-      <c r="F223" s="3">
+      <c r="F223" s="3" t="s">
+        <v>713</v>
+      </c>
+      <c r="G223" s="3">
         <v>1303</v>
       </c>
-      <c r="G223" s="3">
+      <c r="H223" s="3">
         <v>3925</v>
       </c>
-      <c r="H223" s="3"/>
       <c r="I223" s="3"/>
-      <c r="J223" s="3" t="s">
+      <c r="J223" s="3"/>
+      <c r="K223" s="3" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="224" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A224" s="3">
         <v>4018190938</v>
       </c>
@@ -8826,19 +9559,22 @@
       <c r="E224" s="3">
         <v>9708187001</v>
       </c>
-      <c r="F224" s="3">
+      <c r="F224" s="3" t="s">
+        <v>716</v>
+      </c>
+      <c r="G224" s="3">
         <v>825</v>
       </c>
-      <c r="G224" s="3">
+      <c r="H224" s="3">
         <v>3924</v>
       </c>
-      <c r="H224" s="3"/>
       <c r="I224" s="3"/>
-      <c r="J224" s="3" t="s">
+      <c r="J224" s="3"/>
+      <c r="K224" s="3" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="225" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A225" s="3">
         <v>4150419983</v>
       </c>
@@ -8854,19 +9590,22 @@
       <c r="E225" s="3">
         <v>9334124928</v>
       </c>
-      <c r="F225" s="3">
+      <c r="F225" s="3" t="s">
+        <v>713</v>
+      </c>
+      <c r="G225" s="3">
         <v>1303</v>
       </c>
-      <c r="G225" s="3">
+      <c r="H225" s="3">
         <v>3953</v>
       </c>
-      <c r="H225" s="3"/>
       <c r="I225" s="3"/>
-      <c r="J225" s="3" t="s">
+      <c r="J225" s="3"/>
+      <c r="K225" s="3" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="226" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A226" s="3">
         <v>5710525106</v>
       </c>
@@ -8880,19 +9619,22 @@
       <c r="E226" s="3">
         <v>8862924362</v>
       </c>
-      <c r="F226" s="3">
+      <c r="F226" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="G226" s="3">
         <v>823</v>
       </c>
-      <c r="G226" s="3">
+      <c r="H226" s="3">
         <v>3939</v>
       </c>
-      <c r="H226" s="3"/>
       <c r="I226" s="3"/>
-      <c r="J226" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="227" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J226" s="3"/>
+      <c r="K226" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="227" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A227" s="3">
         <v>5260582865</v>
       </c>
@@ -8906,19 +9648,22 @@
       <c r="E227" s="3">
         <v>8102920303</v>
       </c>
-      <c r="F227" s="3">
+      <c r="F227" s="3" t="s">
+        <v>713</v>
+      </c>
+      <c r="G227" s="3">
         <v>870</v>
       </c>
-      <c r="G227" s="3">
+      <c r="H227" s="3">
         <v>3960</v>
       </c>
-      <c r="H227" s="3"/>
       <c r="I227" s="3"/>
-      <c r="J227" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="228" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J227" s="3"/>
+      <c r="K227" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="228" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A228" s="3">
         <v>5885562972</v>
       </c>
@@ -8934,19 +9679,22 @@
       <c r="E228" s="3">
         <v>9334382195</v>
       </c>
-      <c r="F228" s="3">
+      <c r="F228" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="G228" s="3">
         <v>816</v>
       </c>
-      <c r="G228" s="3">
+      <c r="H228" s="3">
         <v>3946</v>
       </c>
-      <c r="H228" s="3"/>
       <c r="I228" s="3"/>
-      <c r="J228" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="229" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J228" s="3"/>
+      <c r="K228" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="229" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A229" s="3">
         <v>6526924620</v>
       </c>
@@ -8962,21 +9710,24 @@
       <c r="E229" s="3">
         <v>9304910692</v>
       </c>
-      <c r="F229" s="3">
+      <c r="F229" s="3" t="s">
+        <v>711</v>
+      </c>
+      <c r="G229" s="3">
         <v>4011</v>
       </c>
-      <c r="G229" s="3">
+      <c r="H229" s="3">
         <v>3833</v>
       </c>
-      <c r="H229" s="3" t="s">
+      <c r="I229" s="3" t="s">
         <v>499</v>
       </c>
-      <c r="I229" s="3"/>
-      <c r="J229" s="3" t="s">
+      <c r="J229" s="3"/>
+      <c r="K229" s="3" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="230" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A230" s="3">
         <v>3091264700</v>
       </c>
@@ -8992,19 +9743,22 @@
       <c r="E230" s="3">
         <v>9334895959</v>
       </c>
-      <c r="F230" s="3">
+      <c r="F230" s="3" t="s">
+        <v>713</v>
+      </c>
+      <c r="G230" s="3">
         <v>1303</v>
       </c>
-      <c r="G230" s="3">
+      <c r="H230" s="3">
         <v>3956</v>
       </c>
-      <c r="H230" s="3"/>
       <c r="I230" s="3"/>
-      <c r="J230" s="3" t="s">
+      <c r="J230" s="3"/>
+      <c r="K230" s="3" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="231" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A231" s="3">
         <v>8942338385</v>
       </c>
@@ -9020,19 +9774,22 @@
       <c r="E231" s="3">
         <v>7645803292</v>
       </c>
-      <c r="F231" s="3">
+      <c r="F231" s="3" t="s">
+        <v>723</v>
+      </c>
+      <c r="G231" s="3">
         <v>801</v>
       </c>
-      <c r="G231" s="3">
+      <c r="H231" s="3">
         <v>3977</v>
       </c>
-      <c r="H231" s="3"/>
       <c r="I231" s="3"/>
-      <c r="J231" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="232" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J231" s="3"/>
+      <c r="K231" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="232" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A232" s="3">
         <v>5648911485</v>
       </c>
@@ -9048,19 +9805,22 @@
       <c r="E232" s="3">
         <v>9334526886</v>
       </c>
-      <c r="F232" s="3">
+      <c r="F232" s="3" t="s">
+        <v>713</v>
+      </c>
+      <c r="G232" s="3">
         <v>1303</v>
       </c>
-      <c r="G232" s="3">
+      <c r="H232" s="3">
         <v>3967</v>
       </c>
-      <c r="H232" s="3"/>
       <c r="I232" s="3"/>
-      <c r="J232" s="3" t="s">
+      <c r="J232" s="3"/>
+      <c r="K232" s="3" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="233" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A233" s="3">
         <v>7027436764</v>
       </c>
@@ -9076,21 +9836,24 @@
       <c r="E233" s="3">
         <v>9835383715</v>
       </c>
-      <c r="F233" s="3">
+      <c r="F233" s="3" t="s">
+        <v>711</v>
+      </c>
+      <c r="G233" s="3">
         <v>844</v>
       </c>
-      <c r="G233" s="3">
+      <c r="H233" s="3">
         <v>3964</v>
       </c>
-      <c r="H233" s="3" t="s">
+      <c r="I233" s="3" t="s">
         <v>542</v>
       </c>
-      <c r="I233" s="3"/>
-      <c r="J233" s="3" t="s">
+      <c r="J233" s="3"/>
+      <c r="K233" s="3" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="234" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A234" s="3">
         <v>6721148115</v>
       </c>
@@ -9106,21 +9869,24 @@
       <c r="E234" s="3">
         <v>9234757747</v>
       </c>
-      <c r="F234" s="3">
+      <c r="F234" s="3" t="s">
+        <v>711</v>
+      </c>
+      <c r="G234" s="3">
         <v>844</v>
       </c>
-      <c r="G234" s="3">
+      <c r="H234" s="3">
         <v>3973</v>
       </c>
-      <c r="H234" s="3" t="s">
+      <c r="I234" s="3" t="s">
         <v>544</v>
       </c>
-      <c r="I234" s="3"/>
-      <c r="J234" s="3" t="s">
+      <c r="J234" s="3"/>
+      <c r="K234" s="3" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="235" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A235" s="3">
         <v>6834570680</v>
       </c>
@@ -9134,19 +9900,22 @@
       <c r="E235" s="3">
         <v>7004226295</v>
       </c>
-      <c r="F235" s="3">
+      <c r="F235" s="3" t="s">
+        <v>722</v>
+      </c>
+      <c r="G235" s="3">
         <v>877</v>
       </c>
-      <c r="G235" s="3">
+      <c r="H235" s="3">
         <v>3987</v>
       </c>
-      <c r="H235" s="3"/>
       <c r="I235" s="3"/>
-      <c r="J235" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="236" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J235" s="3"/>
+      <c r="K235" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="236" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A236" s="3">
         <v>6880049887</v>
       </c>
@@ -9162,19 +9931,22 @@
       <c r="E236" s="3">
         <v>7903094603</v>
       </c>
-      <c r="F236" s="3">
+      <c r="F236" s="3" t="s">
+        <v>713</v>
+      </c>
+      <c r="G236" s="3">
         <v>882</v>
       </c>
-      <c r="G236" s="3">
+      <c r="H236" s="3">
         <v>3802</v>
       </c>
-      <c r="H236" s="3"/>
       <c r="I236" s="3"/>
-      <c r="J236" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="237" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J236" s="3"/>
+      <c r="K236" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="237" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A237" s="3">
         <v>6858585919</v>
       </c>
@@ -9190,21 +9962,24 @@
       <c r="E237" s="3">
         <v>9386868951</v>
       </c>
-      <c r="F237" s="3">
+      <c r="F237" s="3" t="s">
+        <v>714</v>
+      </c>
+      <c r="G237" s="3">
         <v>886</v>
       </c>
-      <c r="G237" s="3">
+      <c r="H237" s="3">
         <v>128</v>
       </c>
-      <c r="H237" s="3" t="s">
+      <c r="I237" s="3" t="s">
         <v>546</v>
       </c>
-      <c r="I237" s="3"/>
-      <c r="J237" s="3" t="s">
+      <c r="J237" s="3"/>
+      <c r="K237" s="3" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="238" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A238" s="3">
         <v>4022426323</v>
       </c>
@@ -9220,21 +9995,24 @@
       <c r="E238" s="3">
         <v>9308545721</v>
       </c>
-      <c r="F238" s="3">
+      <c r="F238" s="3" t="s">
+        <v>711</v>
+      </c>
+      <c r="G238" s="3">
         <v>890</v>
       </c>
-      <c r="G238" s="3">
+      <c r="H238" s="3">
         <v>124</v>
       </c>
-      <c r="H238" s="3" t="s">
+      <c r="I238" s="3" t="s">
         <v>492</v>
       </c>
-      <c r="I238" s="3"/>
-      <c r="J238" s="3" t="s">
+      <c r="J238" s="3"/>
+      <c r="K238" s="3" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="239" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A239" s="3">
         <v>7489190652</v>
       </c>
@@ -9250,19 +10028,22 @@
       <c r="E239" s="3">
         <v>9546314133</v>
       </c>
-      <c r="F239" s="3">
+      <c r="F239" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="G239" s="3">
         <v>1221</v>
       </c>
-      <c r="G239" s="3">
+      <c r="H239" s="3">
         <v>3847</v>
       </c>
-      <c r="H239" s="3"/>
       <c r="I239" s="3"/>
-      <c r="J239" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="240" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J239" s="3"/>
+      <c r="K239" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="240" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A240" s="3">
         <v>1921163791</v>
       </c>
@@ -9278,19 +10059,22 @@
       <c r="E240" s="3">
         <v>9931716646</v>
       </c>
-      <c r="F240" s="3">
+      <c r="F240" s="3" t="s">
+        <v>723</v>
+      </c>
+      <c r="G240" s="3">
         <v>801</v>
       </c>
-      <c r="G240" s="3">
+      <c r="H240" s="3">
         <v>3977</v>
       </c>
-      <c r="H240" s="3"/>
       <c r="I240" s="3"/>
-      <c r="J240" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="241" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J240" s="3"/>
+      <c r="K240" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="241" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A241" s="3">
         <v>1389751081</v>
       </c>
@@ -9306,19 +10090,22 @@
       <c r="E241" s="3">
         <v>9431124044</v>
       </c>
-      <c r="F241" s="3">
+      <c r="F241" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="G241" s="3">
         <v>1221</v>
       </c>
-      <c r="G241" s="3">
+      <c r="H241" s="3">
         <v>3807</v>
       </c>
-      <c r="H241" s="3"/>
       <c r="I241" s="3"/>
-      <c r="J241" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="242" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J241" s="3"/>
+      <c r="K241" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="242" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A242" s="3">
         <v>3990135391</v>
       </c>
@@ -9334,21 +10121,24 @@
       <c r="E242" s="3">
         <v>9939185246</v>
       </c>
-      <c r="F242" s="3">
+      <c r="F242" s="3" t="s">
+        <v>711</v>
+      </c>
+      <c r="G242" s="3">
         <v>844</v>
       </c>
-      <c r="G242" s="3">
+      <c r="H242" s="3">
         <v>119</v>
       </c>
-      <c r="H242" s="3" t="s">
+      <c r="I242" s="3" t="s">
         <v>549</v>
       </c>
-      <c r="I242" s="3"/>
-      <c r="J242" s="3" t="s">
+      <c r="J242" s="3"/>
+      <c r="K242" s="3" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="243" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A243" s="3">
         <v>8114768328</v>
       </c>
@@ -9364,19 +10154,22 @@
       <c r="E243" s="3">
         <v>7283000771</v>
       </c>
-      <c r="F243" s="3">
+      <c r="F243" s="3" t="s">
+        <v>713</v>
+      </c>
+      <c r="G243" s="3">
         <v>870</v>
       </c>
-      <c r="G243" s="3">
+      <c r="H243" s="3">
         <v>3993</v>
       </c>
-      <c r="H243" s="3"/>
       <c r="I243" s="3"/>
-      <c r="J243" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="244" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J243" s="3"/>
+      <c r="K243" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="244" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A244" s="3">
         <v>5754713142</v>
       </c>
@@ -9392,19 +10185,22 @@
       <c r="E244" s="3">
         <v>9693830137</v>
       </c>
-      <c r="F244" s="3">
+      <c r="F244" s="3" t="s">
+        <v>712</v>
+      </c>
+      <c r="G244" s="3">
         <v>1357</v>
       </c>
-      <c r="G244" s="3">
+      <c r="H244" s="3">
         <v>201</v>
       </c>
-      <c r="H244" s="3"/>
       <c r="I244" s="3"/>
-      <c r="J244" s="3" t="s">
+      <c r="J244" s="3"/>
+      <c r="K244" s="3" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="245" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A245" s="3">
         <v>6642826490</v>
       </c>
@@ -9420,21 +10216,24 @@
       <c r="E245" s="3">
         <v>8083832727</v>
       </c>
-      <c r="F245" s="3">
+      <c r="F245" s="3" t="s">
+        <v>714</v>
+      </c>
+      <c r="G245" s="3">
         <v>889</v>
       </c>
-      <c r="G245" s="3">
+      <c r="H245" s="3">
         <v>126</v>
       </c>
-      <c r="H245" s="3" t="s">
+      <c r="I245" s="3" t="s">
         <v>551</v>
       </c>
-      <c r="I245" s="3"/>
-      <c r="J245" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="246" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J245" s="3"/>
+      <c r="K245" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="246" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A246" s="3">
         <v>5108081832</v>
       </c>
@@ -9448,19 +10247,22 @@
       <c r="E246" s="3">
         <v>8210166635</v>
       </c>
-      <c r="F246" s="3">
+      <c r="F246" s="3" t="s">
+        <v>712</v>
+      </c>
+      <c r="G246" s="3">
         <v>1357</v>
       </c>
-      <c r="G246" s="3">
+      <c r="H246" s="3">
         <v>3206</v>
       </c>
-      <c r="H246" s="3"/>
       <c r="I246" s="3"/>
-      <c r="J246" s="3" t="s">
+      <c r="J246" s="3"/>
+      <c r="K246" s="3" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="247" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A247" s="3">
         <v>2389899098</v>
       </c>
@@ -9476,21 +10278,24 @@
       <c r="E247" s="3">
         <v>7004246328</v>
       </c>
-      <c r="F247" s="3">
+      <c r="F247" s="3" t="s">
+        <v>711</v>
+      </c>
+      <c r="G247" s="3">
         <v>844</v>
       </c>
-      <c r="G247" s="3">
+      <c r="H247" s="3">
         <v>133</v>
       </c>
-      <c r="H247" s="3" t="s">
+      <c r="I247" s="3" t="s">
         <v>553</v>
       </c>
-      <c r="I247" s="3"/>
-      <c r="J247" s="3" t="s">
+      <c r="J247" s="3"/>
+      <c r="K247" s="3" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="248" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A248" s="3">
         <v>2695062234</v>
       </c>
@@ -9506,19 +10311,22 @@
       <c r="E248" s="3">
         <v>9304430777</v>
       </c>
-      <c r="F248" s="3">
+      <c r="F248" s="3" t="s">
+        <v>713</v>
+      </c>
+      <c r="G248" s="3">
         <v>870</v>
       </c>
-      <c r="G248" s="3">
+      <c r="H248" s="3">
         <v>113</v>
       </c>
-      <c r="H248" s="3"/>
       <c r="I248" s="3"/>
-      <c r="J248" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="249" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J248" s="3"/>
+      <c r="K248" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="249" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A249" s="3">
         <v>1860839543</v>
       </c>
@@ -9534,23 +10342,26 @@
       <c r="E249" s="3">
         <v>9204746016</v>
       </c>
-      <c r="F249" s="3">
+      <c r="F249" s="3" t="s">
+        <v>711</v>
+      </c>
+      <c r="G249" s="3">
         <v>844</v>
       </c>
-      <c r="G249" s="3">
+      <c r="H249" s="3">
         <v>3994</v>
       </c>
-      <c r="H249" s="3" t="s">
+      <c r="I249" s="3" t="s">
         <v>555</v>
       </c>
-      <c r="I249" s="3" t="s">
+      <c r="J249" s="3" t="s">
         <v>556</v>
       </c>
-      <c r="J249" s="3" t="s">
+      <c r="K249" s="3" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="250" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A250" s="3">
         <v>4943636987</v>
       </c>
@@ -9566,21 +10377,24 @@
       <c r="E250" s="3">
         <v>7870584019</v>
       </c>
-      <c r="F250" s="3">
+      <c r="F250" s="3" t="s">
+        <v>711</v>
+      </c>
+      <c r="G250" s="3">
         <v>832</v>
       </c>
-      <c r="G250" s="3">
+      <c r="H250" s="3">
         <v>3235</v>
       </c>
-      <c r="H250" s="3" t="s">
+      <c r="I250" s="3" t="s">
         <v>558</v>
       </c>
-      <c r="I250" s="3"/>
-      <c r="J250" s="3" t="s">
+      <c r="J250" s="3"/>
+      <c r="K250" s="3" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="251" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A251" s="3">
         <v>4309043662</v>
       </c>
@@ -9596,20 +10410,23 @@
       <c r="E251" s="3">
         <v>9234889460</v>
       </c>
-      <c r="F251" s="3">
+      <c r="F251" s="3" t="s">
+        <v>719</v>
+      </c>
+      <c r="G251" s="3">
         <v>817</v>
       </c>
-      <c r="G251" s="3">
+      <c r="H251" s="3">
         <v>3908</v>
       </c>
-      <c r="H251" s="3"/>
       <c r="I251" s="3"/>
-      <c r="J251" s="3" t="s">
+      <c r="J251" s="3"/>
+      <c r="K251" s="3" t="s">
         <v>256</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J251" xr:uid="{BF083C59-F580-442E-B6A4-AF176C2AA0E1}"/>
+  <autoFilter ref="A1:K251" xr:uid="{BF083C59-F580-442E-B6A4-AF176C2AA0E1}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
